--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Baskonia.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Baskonia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2211.08</v>
+        <v>2523.64</v>
       </c>
       <c r="C2" t="n">
-        <v>2210.34</v>
+        <v>2525.3</v>
       </c>
       <c r="D2" t="n">
-        <v>117.1313010668042</v>
+        <v>118.6789688353859</v>
       </c>
       <c r="E2" t="n">
-        <v>110.5259824280427</v>
+        <v>110.0067318734408</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5610094287298946</v>
+        <v>0.5681159420289855</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1547331552769204</v>
+        <v>0.1509293888585396</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3023983315954119</v>
+        <v>0.304029304029304</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3139212423738214</v>
+        <v>0.3115942028985507</v>
       </c>
       <c r="J2" t="n">
-        <v>342</v>
+        <v>399</v>
       </c>
       <c r="K2" t="n">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="L2" t="n">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="M2" t="n">
-        <v>367</v>
+        <v>410</v>
       </c>
       <c r="N2" t="n">
-        <v>897</v>
+        <v>1027</v>
       </c>
       <c r="O2" t="n">
-        <v>1132</v>
+        <v>1293</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6278424847476428</v>
+        <v>0.6246376811594203</v>
       </c>
       <c r="Q2" t="n">
-        <v>186</v>
+        <v>217</v>
       </c>
       <c r="R2" t="n">
-        <v>376</v>
+        <v>431</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2085413200221853</v>
+        <v>0.2082125603864734</v>
       </c>
       <c r="T2" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="U2" t="n">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1314475873544093</v>
+        <v>0.1289855072463768</v>
       </c>
       <c r="W2" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="X2" t="n">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1031613976705491</v>
+        <v>0.1009661835748792</v>
       </c>
       <c r="Z2" t="n">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="AA2" t="n">
-        <v>579</v>
+        <v>676</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3211314475873544</v>
+        <v>0.3265700483091787</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7924028268551236</v>
+        <v>0.794276875483372</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.5034802784222738</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3206751054852321</v>
+        <v>0.3183520599250936</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.3875598086124402</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3523316062176166</v>
+        <v>0.3653846153846154</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.584805653710247</v>
+        <v>1.588553750966744</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6413502109704642</v>
+        <v>0.6367041198501873</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.094117647058824</v>
+        <v>1.111864406779661</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.95</v>
+        <v>0.9661016949152542</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.044827586206897</v>
+        <v>1.033132530120482</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.627906976744186</v>
+        <v>1.610738255033557</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.250645994832041</v>
+        <v>1.283062645011601</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.658914728682171</v>
+        <v>4.802784222737819</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.909560723514212</v>
+        <v>6.08584686774942</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.96714285714286</v>
+        <v>78.86375</v>
       </c>
       <c r="C3" t="n">
-        <v>78.94071428571429</v>
+        <v>78.91562500000001</v>
       </c>
       <c r="D3" t="n">
-        <v>117.1313010668042</v>
+        <v>118.6789688353859</v>
       </c>
       <c r="E3" t="n">
-        <v>110.5259824280427</v>
+        <v>110.0067318734408</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5610094287298947</v>
+        <v>0.5681159420289855</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1547331552769204</v>
+        <v>0.1509293888585396</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3023983315954119</v>
+        <v>0.304029304029304</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3139212423738215</v>
+        <v>0.3115942028985507</v>
       </c>
       <c r="J3" t="n">
-        <v>12.21428571428571</v>
+        <v>12.46875</v>
       </c>
       <c r="K3" t="n">
-        <v>10.82142857142857</v>
+        <v>10.71875</v>
       </c>
       <c r="L3" t="n">
         <v>7.5</v>
       </c>
       <c r="M3" t="n">
-        <v>13.10714285714286</v>
+        <v>12.8125</v>
       </c>
       <c r="N3" t="n">
-        <v>32.03571428571428</v>
+        <v>32.09375</v>
       </c>
       <c r="O3" t="n">
-        <v>40.42857142857143</v>
+        <v>40.40625</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6278424847476429</v>
+        <v>0.6246376811594203</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.642857142857143</v>
+        <v>6.78125</v>
       </c>
       <c r="R3" t="n">
-        <v>13.42857142857143</v>
+        <v>13.46875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2085413200221853</v>
+        <v>0.2082125603864734</v>
       </c>
       <c r="T3" t="n">
-        <v>2.714285714285714</v>
+        <v>2.65625</v>
       </c>
       <c r="U3" t="n">
-        <v>8.464285714285714</v>
+        <v>8.34375</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1314475873544093</v>
+        <v>0.1289855072463768</v>
       </c>
       <c r="W3" t="n">
-        <v>2.678571428571428</v>
+        <v>2.53125</v>
       </c>
       <c r="X3" t="n">
-        <v>6.642857142857143</v>
+        <v>6.53125</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1031613976705491</v>
+        <v>0.1009661835748792</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.285714285714286</v>
+        <v>7.71875</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.67857142857143</v>
+        <v>21.125</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3211314475873544</v>
+        <v>0.3265700483091787</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7924028268551236</v>
+        <v>0.794276875483372</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4946808510638298</v>
+        <v>0.5034802784222738</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3206751054852321</v>
+        <v>0.3183520599250936</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.4032258064516129</v>
+        <v>0.3875598086124402</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3523316062176166</v>
+        <v>0.3653846153846154</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.584805653710247</v>
+        <v>1.588553750966744</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6413502109704642</v>
+        <v>0.6367041198501873</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.094117647058823</v>
+        <v>1.111864406779661</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.95</v>
+        <v>0.9661016949152542</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.044827586206897</v>
+        <v>1.033132530120482</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.627906976744186</v>
+        <v>1.610738255033557</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.250645994832041</v>
+        <v>1.283062645011601</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.65891472868217</v>
+        <v>4.802784222737819</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.909560723514211</v>
+        <v>6.08584686774942</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2209.599999999999</v>
+        <v>2526.959999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>2210.34</v>
+        <v>2525.3</v>
       </c>
       <c r="D4" t="n">
-        <v>110.5259824280427</v>
+        <v>110.0067318734408</v>
       </c>
       <c r="E4" t="n">
-        <v>117.1313010668042</v>
+        <v>118.6789688353859</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5245857830037414</v>
+        <v>0.5220724907063197</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1439078989446754</v>
+        <v>0.1441052910717526</v>
       </c>
       <c r="H4" t="n">
-        <v>0.28515625</v>
+        <v>0.2872881355932204</v>
       </c>
       <c r="I4" t="n">
-        <v>0.256547300908605</v>
+        <v>0.2467472118959108</v>
       </c>
       <c r="J4" t="n">
-        <v>304</v>
+        <v>337</v>
       </c>
       <c r="K4" t="n">
-        <v>300</v>
+        <v>343</v>
       </c>
       <c r="L4" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="M4" t="n">
-        <v>334</v>
+        <v>383</v>
       </c>
       <c r="N4" t="n">
-        <v>795</v>
+        <v>886</v>
       </c>
       <c r="O4" t="n">
-        <v>1022</v>
+        <v>1135</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5462319615179049</v>
+        <v>0.5274163568773235</v>
       </c>
       <c r="Q4" t="n">
-        <v>194</v>
+        <v>239</v>
       </c>
       <c r="R4" t="n">
-        <v>429</v>
+        <v>516</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2292891501870657</v>
+        <v>0.2397769516728624</v>
       </c>
       <c r="T4" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="U4" t="n">
-        <v>339</v>
+        <v>384</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1811865312667023</v>
+        <v>0.1784386617100372</v>
       </c>
       <c r="W4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="X4" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04970603955104223</v>
+        <v>0.04739776951672862</v>
       </c>
       <c r="Z4" t="n">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="AA4" t="n">
-        <v>603</v>
+        <v>699</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3222875467664351</v>
+        <v>0.324814126394052</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7778864970645792</v>
+        <v>0.7806167400881058</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4522144522144522</v>
+        <v>0.4631782945736434</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3539823008849557</v>
+        <v>0.359375</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4301075268817204</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3233830845771145</v>
+        <v>0.3133047210300429</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.555772994129158</v>
+        <v>1.561233480176212</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7079646017699115</v>
+        <v>0.71875</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.012931034482759</v>
+        <v>0.9775280898876404</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7855297157622739</v>
+        <v>0.7819025522041764</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.027397260273973</v>
+        <v>1.011799410029498</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.666666666666667</v>
+        <v>1.682242990654206</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.305555555555556</v>
+        <v>1.295399515738499</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.197222222222222</v>
+        <v>5.210653753026635</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.502777777777778</v>
+        <v>6.506053268765133</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.9142857142857</v>
+        <v>78.96749999999997</v>
       </c>
       <c r="C5" t="n">
-        <v>78.94071428571429</v>
+        <v>78.91562500000001</v>
       </c>
       <c r="D5" t="n">
-        <v>110.5259824280427</v>
+        <v>110.0067318734408</v>
       </c>
       <c r="E5" t="n">
-        <v>117.1313010668042</v>
+        <v>118.6789688353859</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5245857830037414</v>
+        <v>0.5220724907063197</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1439078989446754</v>
+        <v>0.1441052910717526</v>
       </c>
       <c r="H5" t="n">
-        <v>0.28515625</v>
+        <v>0.2872881355932204</v>
       </c>
       <c r="I5" t="n">
-        <v>0.256547300908605</v>
+        <v>0.2467472118959108</v>
       </c>
       <c r="J5" t="n">
-        <v>10.85714285714286</v>
+        <v>10.53125</v>
       </c>
       <c r="K5" t="n">
-        <v>10.71428571428571</v>
+        <v>10.71875</v>
       </c>
       <c r="L5" t="n">
-        <v>5.357142857142857</v>
+        <v>5.625</v>
       </c>
       <c r="M5" t="n">
-        <v>11.92857142857143</v>
+        <v>11.96875</v>
       </c>
       <c r="N5" t="n">
-        <v>28.39285714285714</v>
+        <v>27.6875</v>
       </c>
       <c r="O5" t="n">
-        <v>36.5</v>
+        <v>35.46875</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5462319615179049</v>
+        <v>0.5274163568773235</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.928571428571429</v>
+        <v>7.46875</v>
       </c>
       <c r="R5" t="n">
-        <v>15.32142857142857</v>
+        <v>16.125</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2292891501870657</v>
+        <v>0.2397769516728624</v>
       </c>
       <c r="T5" t="n">
-        <v>4.285714285714286</v>
+        <v>4.3125</v>
       </c>
       <c r="U5" t="n">
-        <v>12.10714285714286</v>
+        <v>12</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1811865312667023</v>
+        <v>0.1784386617100372</v>
       </c>
       <c r="W5" t="n">
-        <v>1.428571428571429</v>
+        <v>1.3125</v>
       </c>
       <c r="X5" t="n">
-        <v>3.321428571428572</v>
+        <v>3.1875</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04970603955104223</v>
+        <v>0.04739776951672862</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.964285714285714</v>
+        <v>6.84375</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.53571428571428</v>
+        <v>21.84375</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3222875467664351</v>
+        <v>0.324814126394052</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7778864970645792</v>
+        <v>0.7806167400881058</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4522144522144522</v>
+        <v>0.4631782945736434</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3539823008849557</v>
+        <v>0.359375</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4301075268817204</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3233830845771145</v>
+        <v>0.3133047210300429</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.555772994129158</v>
+        <v>1.561233480176212</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7079646017699115</v>
+        <v>0.71875</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.012931034482758</v>
+        <v>0.9775280898876404</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7855297157622739</v>
+        <v>0.7819025522041764</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.027397260273972</v>
+        <v>1.011799410029498</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.666666666666667</v>
+        <v>1.682242990654206</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.305555555555555</v>
+        <v>1.295399515738499</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.197222222222222</v>
+        <v>5.210653753026635</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.502777777777778</v>
+        <v>6.506053268765133</v>
       </c>
     </row>
     <row r="7">
@@ -1419,28 +1419,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G8" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H8" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J8" t="n">
         <v>17</v>
@@ -1452,7 +1452,7 @@
         <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N8" t="n">
         <v>3</v>
@@ -1461,22 +1461,22 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Q8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R8" t="n">
         <v>20</v>
       </c>
       <c r="S8" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T8" t="n">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="U8" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="V8" t="n">
         <v>17</v>
@@ -1488,22 +1488,22 @@
         <v>7</v>
       </c>
       <c r="Y8" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.945</v>
+        <v>0.93</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.533</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AE8" t="n">
         <v>4</v>
@@ -1518,57 +1518,57 @@
         <v>5</v>
       </c>
       <c r="AI8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.333</v>
+        <v>0.312</v>
       </c>
       <c r="AK8" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.349</v>
+        <v>0.384</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>256:40</t>
+          <t>277:14</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>160.36</v>
+        <v>175.24</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.552</v>
+        <v>0.579</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.625</v>
+        <v>0.642</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.048</v>
+        <v>1.079</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.162</v>
+        <v>0.16</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.357</v>
+        <v>0.331</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.654</v>
+        <v>0.607</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.28</v>
+        <v>0.283</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.021</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="9">
@@ -1578,156 +1578,156 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E9" t="n">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F9" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
+        <v>69</v>
+      </c>
+      <c r="H9" t="n">
         <v>56</v>
       </c>
-      <c r="H9" t="n">
-        <v>53</v>
-      </c>
       <c r="I9" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J9" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K9" t="n">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="L9" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N9" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Q9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R9" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="S9" t="n">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="T9" t="n">
-        <v>334</v>
+        <v>389</v>
       </c>
       <c r="U9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="V9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="W9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Y9" t="n">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="Z9" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.777</v>
+        <v>0.776</v>
       </c>
       <c r="AB9" t="n">
         <v>21</v>
       </c>
       <c r="AC9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.618</v>
+        <v>0.6</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.308</v>
+        <v>0.286</v>
       </c>
       <c r="AH9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.316</v>
+        <v>0.348</v>
       </c>
       <c r="AK9" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.351</v>
+        <v>0.37</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>547:55</t>
+          <t>631:14</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>225.36</v>
+        <v>252.56</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.619</v>
+        <v>0.628</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.659</v>
+        <v>0.663</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.136</v>
+        <v>1.152</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.138</v>
+        <v>0.131</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.323</v>
+        <v>0.299</v>
       </c>
       <c r="AU9" t="n">
-        <v>1</v>
+        <v>1.152</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.184</v>
+        <v>0.179</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.09</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.156</v>
+        <v>0.167</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.04</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="10">
@@ -1737,156 +1737,156 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>24</v>
+      </c>
+      <c r="C10" t="n">
+        <v>306</v>
+      </c>
+      <c r="D10" t="n">
+        <v>76</v>
+      </c>
+      <c r="E10" t="n">
+        <v>122</v>
+      </c>
+      <c r="F10" t="n">
+        <v>36</v>
+      </c>
+      <c r="G10" t="n">
+        <v>88</v>
+      </c>
+      <c r="H10" t="n">
+        <v>46</v>
+      </c>
+      <c r="I10" t="n">
+        <v>59</v>
+      </c>
+      <c r="J10" t="n">
+        <v>60</v>
+      </c>
+      <c r="K10" t="n">
+        <v>44</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>15</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>40</v>
+      </c>
+      <c r="R10" t="n">
+        <v>76</v>
+      </c>
+      <c r="S10" t="n">
+        <v>57</v>
+      </c>
+      <c r="T10" t="n">
+        <v>272</v>
+      </c>
+      <c r="U10" t="n">
+        <v>34</v>
+      </c>
+      <c r="V10" t="n">
+        <v>25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>26</v>
+      </c>
+      <c r="X10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>86</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>111</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF10" t="n">
         <v>20</v>
       </c>
-      <c r="C10" t="n">
-        <v>247</v>
-      </c>
-      <c r="D10" t="n">
-        <v>61</v>
-      </c>
-      <c r="E10" t="n">
-        <v>102</v>
-      </c>
-      <c r="F10" t="n">
-        <v>29</v>
-      </c>
-      <c r="G10" t="n">
-        <v>69</v>
-      </c>
-      <c r="H10" t="n">
-        <v>38</v>
-      </c>
-      <c r="I10" t="n">
-        <v>50</v>
-      </c>
-      <c r="J10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K10" t="n">
-        <v>34</v>
-      </c>
-      <c r="L10" t="n">
-        <v>8</v>
-      </c>
-      <c r="M10" t="n">
-        <v>12</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>34</v>
-      </c>
-      <c r="R10" t="n">
-        <v>65</v>
-      </c>
-      <c r="S10" t="n">
-        <v>47</v>
-      </c>
-      <c r="T10" t="n">
-        <v>210</v>
-      </c>
-      <c r="U10" t="n">
-        <v>25</v>
-      </c>
-      <c r="V10" t="n">
-        <v>23</v>
-      </c>
-      <c r="W10" t="n">
-        <v>22</v>
-      </c>
-      <c r="X10" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>71</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.747</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>41</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>16</v>
-      </c>
       <c r="AG10" t="n">
-        <v>0.375</v>
+        <v>0.35</v>
       </c>
       <c r="AH10" t="n">
         <v>7</v>
       </c>
       <c r="AI10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.467</v>
+        <v>0.412</v>
       </c>
       <c r="AK10" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AL10" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.407</v>
+        <v>0.408</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>443:00</t>
+          <t>534:52</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>227</v>
+        <v>275.96</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.611</v>
+        <v>0.619</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.64</v>
+        <v>0.648</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.088</v>
+        <v>1.109</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.15</v>
+        <v>0.145</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.222</v>
+        <v>0.219</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.471</v>
+        <v>1.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.229</v>
+        <v>0.231</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.021</v>
+        <v>0.022</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.089</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.064</v>
+        <v>0.067</v>
       </c>
     </row>
     <row r="11">
@@ -2036,16 +2036,16 @@
         <v>1.467</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.245</v>
+        <v>0.246</v>
       </c>
       <c r="AW11" t="n">
         <v>0.053</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.108</v>
+        <v>0.107</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.026</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="12">
@@ -2055,43 +2055,43 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J12" t="n">
+        <v>42</v>
+      </c>
+      <c r="K12" t="n">
         <v>35</v>
       </c>
-      <c r="K12" t="n">
-        <v>31</v>
-      </c>
       <c r="L12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M12" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2103,52 +2103,52 @@
         <v>17</v>
       </c>
       <c r="R12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="S12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="T12" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="U12" t="n">
         <v>6</v>
       </c>
       <c r="V12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W12" t="n">
+        <v>12</v>
+      </c>
+      <c r="X12" t="n">
         <v>8</v>
       </c>
-      <c r="X12" t="n">
-        <v>5</v>
-      </c>
       <c r="Y12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Z12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.763</v>
+        <v>0.78</v>
       </c>
       <c r="AB12" t="n">
         <v>7</v>
       </c>
       <c r="AC12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.5</v>
+        <v>0.438</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.4</v>
+        <v>0.429</v>
       </c>
       <c r="AH12" t="n">
         <v>2</v>
@@ -2163,48 +2163,48 @@
         <v>3</v>
       </c>
       <c r="AL12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.429</v>
+        <v>0.3</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>356:13</t>
+          <t>402:14</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>74.68000000000001</v>
+        <v>83.56</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.635</v>
+        <v>0.58</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.659</v>
+        <v>0.616</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.018</v>
+        <v>0.981</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.228</v>
+        <v>0.203</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.312</v>
+        <v>0.304</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.059</v>
+        <v>2.471</v>
       </c>
       <c r="AV12" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AX12" t="n">
         <v>0.094</v>
       </c>
-      <c r="AW12" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0.095</v>
-      </c>
       <c r="AY12" t="n">
-        <v>0.041</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="13">
@@ -2214,156 +2214,156 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>23</v>
+      </c>
+      <c r="C13" t="n">
+        <v>185</v>
+      </c>
+      <c r="D13" t="n">
+        <v>54</v>
+      </c>
+      <c r="E13" t="n">
+        <v>81</v>
+      </c>
+      <c r="F13" t="n">
+        <v>13</v>
+      </c>
+      <c r="G13" t="n">
+        <v>39</v>
+      </c>
+      <c r="H13" t="n">
+        <v>38</v>
+      </c>
+      <c r="I13" t="n">
+        <v>51</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34</v>
+      </c>
+      <c r="K13" t="n">
+        <v>37</v>
+      </c>
+      <c r="L13" t="n">
+        <v>18</v>
+      </c>
+      <c r="M13" t="n">
         <v>19</v>
       </c>
-      <c r="C13" t="n">
-        <v>141</v>
-      </c>
-      <c r="D13" t="n">
-        <v>43</v>
-      </c>
-      <c r="E13" t="n">
-        <v>63</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="N13" t="n">
         <v>9</v>
       </c>
-      <c r="G13" t="n">
-        <v>33</v>
-      </c>
-      <c r="H13" t="n">
-        <v>28</v>
-      </c>
-      <c r="I13" t="n">
-        <v>39</v>
-      </c>
-      <c r="J13" t="n">
-        <v>28</v>
-      </c>
-      <c r="K13" t="n">
-        <v>29</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>42</v>
+      </c>
+      <c r="R13" t="n">
+        <v>48</v>
+      </c>
+      <c r="S13" t="n">
+        <v>48</v>
+      </c>
+      <c r="T13" t="n">
+        <v>194</v>
+      </c>
+      <c r="U13" t="n">
+        <v>30</v>
+      </c>
+      <c r="V13" t="n">
+        <v>25</v>
+      </c>
+      <c r="W13" t="n">
         <v>14</v>
       </c>
-      <c r="M13" t="n">
-        <v>16</v>
-      </c>
-      <c r="N13" t="n">
-        <v>6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>36</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>36</v>
-      </c>
-      <c r="R13" t="n">
-        <v>43</v>
-      </c>
-      <c r="S13" t="n">
-        <v>39</v>
-      </c>
-      <c r="T13" t="n">
-        <v>139</v>
-      </c>
-      <c r="U13" t="n">
-        <v>26</v>
-      </c>
-      <c r="V13" t="n">
-        <v>19</v>
-      </c>
-      <c r="W13" t="n">
-        <v>11</v>
-      </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y13" t="n">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="Z13" t="n">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.803</v>
+        <v>0.804</v>
       </c>
       <c r="AB13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AC13" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.381</v>
+        <v>0.444</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="AH13" t="n">
         <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AK13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AL13" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.296</v>
+        <v>0.375</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>308:14</t>
+          <t>363:47</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>149.16</v>
+        <v>184.44</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.589</v>
+        <v>0.612</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.623</v>
+        <v>0.649</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.945</v>
+        <v>1.003</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.241</v>
+        <v>0.228</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.292</v>
+        <v>0.317</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.778</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.217</v>
+        <v>0.227</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.053</v>
+        <v>0.058</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.103</v>
+        <v>0.11</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.034</v>
+        <v>0.036</v>
       </c>
     </row>
     <row r="14">
@@ -2519,10 +2519,10 @@
         <v>0.066</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.234</v>
+        <v>0.232</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="15">
@@ -2532,22 +2532,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="D15" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E15" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="F15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="H15" t="n">
         <v>30</v>
@@ -2556,16 +2556,16 @@
         <v>47</v>
       </c>
       <c r="J15" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="K15" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="L15" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="M15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N15" t="n">
         <v>13</v>
@@ -2574,58 +2574,58 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q15" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R15" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="S15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="T15" t="n">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="U15" t="n">
         <v>22</v>
       </c>
       <c r="V15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="W15" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="X15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Y15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Z15" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="AA15" t="n">
         <v>0.649</v>
       </c>
       <c r="AB15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AC15" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.516</v>
+        <v>0.475</v>
       </c>
       <c r="AE15" t="n">
         <v>3</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AH15" t="n">
         <v>1</v>
@@ -2637,51 +2637,51 @@
         <v>0.333</v>
       </c>
       <c r="AK15" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AL15" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.446</v>
+        <v>0.433</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>395:38</t>
+          <t>476:07</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>180.68</v>
+        <v>209.68</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.58</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.6</v>
+        <v>0.581</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.007</v>
+        <v>0.973</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.161</v>
+        <v>0.162</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.229</v>
+        <v>0.194</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.172</v>
+        <v>1.176</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.205</v>
+        <v>0.197</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.077</v>
+        <v>0.074</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.163</v>
+        <v>0.155</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="16">
@@ -2691,67 +2691,67 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" t="n">
+        <v>59</v>
+      </c>
+      <c r="D16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" t="n">
+        <v>22</v>
+      </c>
+      <c r="F16" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" t="n">
+        <v>21</v>
+      </c>
+      <c r="H16" t="n">
         <v>8</v>
       </c>
-      <c r="C16" t="n">
-        <v>48</v>
-      </c>
-      <c r="D16" t="n">
-        <v>12</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="I16" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" t="n">
+        <v>28</v>
+      </c>
+      <c r="L16" t="n">
+        <v>11</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
         <v>15</v>
       </c>
-      <c r="F16" t="n">
-        <v>6</v>
-      </c>
-      <c r="G16" t="n">
-        <v>20</v>
-      </c>
-      <c r="H16" t="n">
-        <v>6</v>
-      </c>
-      <c r="I16" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" t="n">
-        <v>9</v>
-      </c>
-      <c r="K16" t="n">
-        <v>19</v>
-      </c>
-      <c r="L16" t="n">
-        <v>9</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>3</v>
-      </c>
-      <c r="R16" t="n">
-        <v>11</v>
-      </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="U16" t="n">
         <v>2</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
         <v>4</v>
@@ -2760,40 +2760,40 @@
         <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.929</v>
+        <v>0.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AD16" t="n">
         <v>0.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.167</v>
+        <v>0.286</v>
       </c>
       <c r="AK16" t="n">
         <v>5</v>
@@ -2806,41 +2806,41 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>133:45</t>
+          <t>164:14</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>41.08</v>
+        <v>52.84</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.6</v>
+        <v>0.593</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.63</v>
+        <v>0.617</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.168</v>
+        <v>1.117</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.073</v>
+        <v>0.095</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.171</v>
+        <v>0.186</v>
       </c>
       <c r="AU16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.138</v>
+        <v>0.144</v>
       </c>
       <c r="AW16" t="n">
         <v>0.079</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.155</v>
+        <v>0.185</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="17">
@@ -2850,156 +2850,156 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C17" t="n">
-        <v>474</v>
+        <v>555</v>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E17" t="n">
+        <v>162</v>
+      </c>
+      <c r="F17" t="n">
+        <v>81</v>
+      </c>
+      <c r="G17" t="n">
+        <v>206</v>
+      </c>
+      <c r="H17" t="n">
         <v>140</v>
       </c>
-      <c r="F17" t="n">
-        <v>70</v>
-      </c>
-      <c r="G17" t="n">
-        <v>174</v>
-      </c>
-      <c r="H17" t="n">
-        <v>118</v>
-      </c>
       <c r="I17" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="J17" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K17" t="n">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="M17" t="n">
+        <v>29</v>
+      </c>
+      <c r="N17" t="n">
+        <v>14</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>45</v>
+      </c>
+      <c r="R17" t="n">
+        <v>68</v>
+      </c>
+      <c r="S17" t="n">
+        <v>113</v>
+      </c>
+      <c r="T17" t="n">
+        <v>546</v>
+      </c>
+      <c r="U17" t="n">
+        <v>68</v>
+      </c>
+      <c r="V17" t="n">
+        <v>61</v>
+      </c>
+      <c r="W17" t="n">
+        <v>41</v>
+      </c>
+      <c r="X17" t="n">
         <v>26</v>
       </c>
-      <c r="N17" t="n">
-        <v>12</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>41</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>41</v>
-      </c>
-      <c r="R17" t="n">
-        <v>64</v>
-      </c>
-      <c r="S17" t="n">
-        <v>94</v>
-      </c>
-      <c r="T17" t="n">
-        <v>469</v>
-      </c>
-      <c r="U17" t="n">
-        <v>56</v>
-      </c>
-      <c r="V17" t="n">
-        <v>55</v>
-      </c>
-      <c r="W17" t="n">
-        <v>38</v>
-      </c>
-      <c r="X17" t="n">
-        <v>24</v>
-      </c>
       <c r="Y17" t="n">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="Z17" t="n">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.867</v>
+        <v>0.861</v>
       </c>
       <c r="AB17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AC17" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.442</v>
+        <v>0.451</v>
       </c>
       <c r="AE17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF17" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.34</v>
+        <v>0.333</v>
       </c>
       <c r="AH17" t="n">
         <v>28</v>
       </c>
       <c r="AI17" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.609</v>
+        <v>0.549</v>
       </c>
       <c r="AK17" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="AL17" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.328</v>
+        <v>0.342</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>601:05</t>
+          <t>693:46</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>412.2</v>
+        <v>481.64</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.638</v>
+        <v>0.636</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.15</v>
+        <v>1.152</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.099</v>
+        <v>0.093</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.376</v>
+        <v>0.38</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.195</v>
+        <v>1.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.307</v>
+        <v>0.311</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.149</v>
+        <v>0.139</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.067</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="18">
@@ -3009,40 +3009,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C18" t="n">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E18" t="n">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H18" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I18" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J18" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="K18" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="L18" t="n">
         <v>13</v>
       </c>
       <c r="M18" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="N18" t="n">
         <v>20</v>
@@ -3051,49 +3051,49 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="Q18" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="R18" t="n">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="S18" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="T18" t="n">
-        <v>249</v>
+        <v>303</v>
       </c>
       <c r="U18" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="V18" t="n">
         <v>24</v>
       </c>
       <c r="W18" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="X18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="Z18" t="n">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.788</v>
+        <v>0.804</v>
       </c>
       <c r="AB18" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AC18" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.4</v>
+        <v>0.436</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3114,48 +3114,48 @@
         <v>0.231</v>
       </c>
       <c r="AK18" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AL18" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.348</v>
+        <v>0.4</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>534:28</t>
+          <t>604:14</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>214.44</v>
+        <v>237.52</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.478</v>
+        <v>0.511</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.534</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.919</v>
+        <v>0.977</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.14</v>
+        <v>0.139</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.259</v>
+        <v>0.274</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.833</v>
+        <v>1.939</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.18</v>
+        <v>0.176</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.028</v>
+        <v>0.025</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.117</v>
+        <v>0.118</v>
       </c>
       <c r="AY18" t="n">
         <v>0.06900000000000001</v>
@@ -3168,156 +3168,156 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>21</v>
+      </c>
+      <c r="C19" t="n">
+        <v>303</v>
+      </c>
+      <c r="D19" t="n">
+        <v>67</v>
+      </c>
+      <c r="E19" t="n">
+        <v>109</v>
+      </c>
+      <c r="F19" t="n">
         <v>18</v>
       </c>
-      <c r="C19" t="n">
-        <v>258</v>
-      </c>
-      <c r="D19" t="n">
-        <v>55</v>
-      </c>
-      <c r="E19" t="n">
-        <v>93</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
+        <v>63</v>
+      </c>
+      <c r="H19" t="n">
+        <v>115</v>
+      </c>
+      <c r="I19" t="n">
+        <v>125</v>
+      </c>
+      <c r="J19" t="n">
+        <v>84</v>
+      </c>
+      <c r="K19" t="n">
+        <v>64</v>
+      </c>
+      <c r="L19" t="n">
+        <v>10</v>
+      </c>
+      <c r="M19" t="n">
+        <v>26</v>
+      </c>
+      <c r="N19" t="n">
+        <v>14</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>42</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>42</v>
+      </c>
+      <c r="R19" t="n">
+        <v>30</v>
+      </c>
+      <c r="S19" t="n">
+        <v>97</v>
+      </c>
+      <c r="T19" t="n">
+        <v>429</v>
+      </c>
+      <c r="U19" t="n">
+        <v>54</v>
+      </c>
+      <c r="V19" t="n">
+        <v>33</v>
+      </c>
+      <c r="W19" t="n">
+        <v>15</v>
+      </c>
+      <c r="X19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>147</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>164</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>53</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI19" t="n">
         <v>16</v>
       </c>
-      <c r="G19" t="n">
-        <v>53</v>
-      </c>
-      <c r="H19" t="n">
-        <v>100</v>
-      </c>
-      <c r="I19" t="n">
-        <v>108</v>
-      </c>
-      <c r="J19" t="n">
-        <v>74</v>
-      </c>
-      <c r="K19" t="n">
-        <v>52</v>
-      </c>
-      <c r="L19" t="n">
-        <v>9</v>
-      </c>
-      <c r="M19" t="n">
-        <v>21</v>
-      </c>
-      <c r="N19" t="n">
-        <v>11</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>35</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>35</v>
-      </c>
-      <c r="R19" t="n">
-        <v>24</v>
-      </c>
-      <c r="S19" t="n">
-        <v>81</v>
-      </c>
-      <c r="T19" t="n">
-        <v>364</v>
-      </c>
-      <c r="U19" t="n">
-        <v>44</v>
-      </c>
-      <c r="V19" t="n">
-        <v>28</v>
-      </c>
-      <c r="W19" t="n">
-        <v>13</v>
-      </c>
-      <c r="X19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>126</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>141</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.894</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.479</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>12</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>0.167</v>
+        <v>0.188</v>
       </c>
       <c r="AK19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL19" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.341</v>
+        <v>0.319</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>460:32</t>
+          <t>534:18</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>228.52</v>
+        <v>269</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.541</v>
+        <v>0.547</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.667</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.129</v>
+        <v>1.126</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.153</v>
+        <v>0.156</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.669</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.114</v>
+        <v>2</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.222</v>
+        <v>0.226</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.023</v>
+        <v>0.022</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.123</v>
+        <v>0.13</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="20">
@@ -3327,67 +3327,67 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
+        <v>58</v>
+      </c>
+      <c r="D20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E20" t="n">
+        <v>37</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>18</v>
+      </c>
+      <c r="I20" t="n">
         <v>34</v>
       </c>
-      <c r="D20" t="n">
-        <v>11</v>
-      </c>
-      <c r="E20" t="n">
-        <v>21</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>12</v>
-      </c>
-      <c r="I20" t="n">
-        <v>23</v>
-      </c>
       <c r="J20" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>24</v>
+      </c>
+      <c r="L20" t="n">
+        <v>19</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="n">
-        <v>13</v>
-      </c>
-      <c r="L20" t="n">
-        <v>7</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R20" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="S20" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="T20" t="n">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="W20" t="n">
         <v>2</v>
@@ -3396,31 +3396,31 @@
         <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="Z20" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.583</v>
+        <v>0.618</v>
       </c>
       <c r="AB20" t="n">
         <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.286</v>
+        <v>0.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH20" t="n">
         <v>0</v>
@@ -3442,41 +3442,41 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>93:33</t>
+          <t>148:48</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>36.12</v>
+        <v>61.96</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.524</v>
+        <v>0.541</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.546</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.138</v>
+        <v>0.161</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.571</v>
+        <v>0.486</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.173</v>
+        <v>0.187</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.152</v>
+        <v>0.175</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="21">
@@ -3486,40 +3486,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G21" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J21" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K21" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N21" t="n">
         <v>4</v>
@@ -3528,111 +3528,111 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R21" t="n">
+        <v>31</v>
+      </c>
+      <c r="S21" t="n">
+        <v>19</v>
+      </c>
+      <c r="T21" t="n">
+        <v>159</v>
+      </c>
+      <c r="U21" t="n">
+        <v>11</v>
+      </c>
+      <c r="V21" t="n">
+        <v>15</v>
+      </c>
+      <c r="W21" t="n">
+        <v>7</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z21" t="n">
         <v>25</v>
       </c>
-      <c r="S21" t="n">
-        <v>17</v>
-      </c>
-      <c r="T21" t="n">
-        <v>143</v>
-      </c>
-      <c r="U21" t="n">
-        <v>8</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="AA21" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC21" t="n">
         <v>13</v>
       </c>
-      <c r="W21" t="n">
-        <v>5</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>11</v>
-      </c>
       <c r="AD21" t="n">
-        <v>0.727</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AE21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI21" t="n">
         <v>16</v>
       </c>
-      <c r="AG21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI21" t="n">
+      <c r="AJ21" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AK21" t="n">
         <v>13</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>12</v>
-      </c>
       <c r="AL21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>364:50</t>
+          <t>432:03</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>95.40000000000001</v>
+        <v>106.28</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.591</v>
+        <v>0.61</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.596</v>
+        <v>0.613</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.017</v>
+        <v>1.054</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.147</v>
+        <v>0.141</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.078</v>
+        <v>0.081</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.714</v>
+        <v>1.867</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.117</v>
+        <v>0.11</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.08</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.141</v>
+        <v>0.128</v>
       </c>
       <c r="AY21" t="n">
         <v>0.029</v>
@@ -3788,13 +3788,13 @@
         <v>0.1</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.089</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.212</v>
+        <v>0.211</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.02</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="23">
@@ -3950,7 +3950,7 @@
         <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.204</v>
+        <v>0.203</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -3963,43 +3963,43 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C24" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D24" t="n">
         <v>20</v>
       </c>
       <c r="E24" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F24" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M24" t="n">
         <v>13</v>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -4011,16 +4011,16 @@
         <v>6</v>
       </c>
       <c r="R24" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="S24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T24" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="U24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V24" t="n">
         <v>30</v>
@@ -4032,13 +4032,13 @@
         <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Z24" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.739</v>
+        <v>0.731</v>
       </c>
       <c r="AB24" t="n">
         <v>9</v>
@@ -4053,63 +4053,63 @@
         <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.133</v>
+        <v>0.118</v>
       </c>
       <c r="AH24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.524</v>
+        <v>0.522</v>
       </c>
       <c r="AK24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL24" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.306</v>
+        <v>0.32</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>381:44</t>
+          <t>415:36</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>128.4</v>
+        <v>135.28</v>
       </c>
       <c r="AP24" t="n">
         <v>0.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.515</v>
+        <v>0.518</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.981</v>
+        <v>0.991</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.047</v>
+        <v>0.044</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.068</v>
+        <v>0.081</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.667</v>
+        <v>2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.151</v>
+        <v>0.146</v>
       </c>
       <c r="AW24" t="n">
-        <v>0.08</v>
+        <v>0.076</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.172</v>
+        <v>0.167</v>
       </c>
       <c r="AY24" t="n">
         <v>0.012</v>
@@ -4281,16 +4281,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -4329,17 +4329,17 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
       </c>
       <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
         <v>2</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
       <c r="V26" t="n">
         <v>0</v>
       </c>
@@ -4350,10 +4350,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="n">
         <v>1</v>
@@ -4396,38 +4396,38 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>2.44</v>
+        <v>3.44</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.615</v>
+        <v>0.727</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.23</v>
+        <v>1.453</v>
       </c>
       <c r="AS26" t="n">
         <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AU26" t="n">
         <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.143</v>
+        <v>0.17</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.153</v>
+        <v>0.129</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.143</v>
+        <v>0.12</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -4586,10 +4586,10 @@
         <v>0.057</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.01</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -4745,7 +4745,7 @@
         <v>0.051</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.142</v>
+        <v>0.141</v>
       </c>
       <c r="AY28" t="n">
         <v>0.002</v>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -4785,10 +4785,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L29" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -4913,157 +4913,157 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>2997</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>684</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1185</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>328</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>885</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>806</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>553</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>841</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>431</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>410</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>703</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>725</v>
       </c>
       <c r="T30" t="n">
-        <v>57</v>
+        <v>3553</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1027</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1293</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>0.794</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>431</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>0.318</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>0.388</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>676</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>6400:00</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>20</v>
+        <v>2855.64</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>0.618</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1.283</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -5072,157 +5072,157 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C31" t="n">
-        <v>2589</v>
+        <v>2778</v>
       </c>
       <c r="D31" t="n">
-        <v>593</v>
+        <v>732</v>
       </c>
       <c r="E31" t="n">
-        <v>1038</v>
+        <v>1351</v>
       </c>
       <c r="F31" t="n">
-        <v>279</v>
+        <v>261</v>
       </c>
       <c r="G31" t="n">
-        <v>765</v>
+        <v>801</v>
       </c>
       <c r="H31" t="n">
-        <v>566</v>
+        <v>531</v>
       </c>
       <c r="I31" t="n">
-        <v>707</v>
+        <v>684</v>
       </c>
       <c r="J31" t="n">
-        <v>484</v>
+        <v>535</v>
       </c>
       <c r="K31" t="n">
-        <v>732</v>
+        <v>760</v>
       </c>
       <c r="L31" t="n">
-        <v>290</v>
+        <v>339</v>
       </c>
       <c r="M31" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N31" t="n">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="Q31" t="n">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="R31" t="n">
-        <v>623</v>
+        <v>736</v>
       </c>
       <c r="S31" t="n">
-        <v>635</v>
+        <v>702</v>
       </c>
       <c r="T31" t="n">
-        <v>3043</v>
+        <v>3073</v>
       </c>
       <c r="U31" t="n">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="V31" t="n">
-        <v>303</v>
+        <v>343</v>
       </c>
       <c r="W31" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="X31" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="Y31" t="n">
-        <v>897</v>
+        <v>886</v>
       </c>
       <c r="Z31" t="n">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.792</v>
+        <v>0.781</v>
       </c>
       <c r="AB31" t="n">
-        <v>186</v>
+        <v>239</v>
       </c>
       <c r="AC31" t="n">
-        <v>376</v>
+        <v>516</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.495</v>
+        <v>0.463</v>
       </c>
       <c r="AE31" t="n">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="AF31" t="n">
-        <v>237</v>
+        <v>384</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.321</v>
+        <v>0.359</v>
       </c>
       <c r="AH31" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AI31" t="n">
-        <v>186</v>
+        <v>102</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.403</v>
+        <v>0.412</v>
       </c>
       <c r="AK31" t="n">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="AL31" t="n">
-        <v>579</v>
+        <v>699</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.352</v>
+        <v>0.313</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>5600:00</t>
+          <t>6400:00</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>2501.08</v>
+        <v>2865.96</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.522</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.612</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.035</v>
+        <v>0.969</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.155</v>
+        <v>0.144</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.314</v>
+        <v>0.247</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.251</v>
+        <v>1.295</v>
       </c>
       <c r="AV31" t="n">
         <v>0.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.06</v>
+        <v>0.057</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.143</v>
+        <v>0.139</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -5231,2963 +5231,2963 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>28</v>
-      </c>
-      <c r="C32" t="n">
-        <v>2443</v>
-      </c>
-      <c r="D32" t="n">
-        <v>629</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1175</v>
-      </c>
-      <c r="F32" t="n">
-        <v>235</v>
-      </c>
-      <c r="G32" t="n">
-        <v>696</v>
-      </c>
-      <c r="H32" t="n">
-        <v>480</v>
-      </c>
-      <c r="I32" t="n">
-        <v>615</v>
-      </c>
-      <c r="J32" t="n">
-        <v>470</v>
-      </c>
-      <c r="K32" t="n">
-        <v>669</v>
-      </c>
-      <c r="L32" t="n">
-        <v>292</v>
-      </c>
-      <c r="M32" t="n">
-        <v>189</v>
-      </c>
-      <c r="N32" t="n">
-        <v>180</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>360</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>334</v>
-      </c>
-      <c r="R32" t="n">
-        <v>645</v>
-      </c>
-      <c r="S32" t="n">
-        <v>622</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2718</v>
-      </c>
-      <c r="U32" t="n">
-        <v>304</v>
-      </c>
-      <c r="V32" t="n">
-        <v>300</v>
-      </c>
-      <c r="W32" t="n">
-        <v>150</v>
-      </c>
-      <c r="X32" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>795</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1022</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>194</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>429</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>339</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>93</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>195</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>603</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>5600:00</t>
-        </is>
-      </c>
-      <c r="AO32" t="n">
-        <v>2501.6</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0.977</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>1.306</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
+          <t>#0 M. HOWARD (Per Game)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>12</v>
+      </c>
+      <c r="C33" t="n">
+        <v>15.75</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G33" t="n">
+        <v>7.417</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T33" t="n">
+        <v>140</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.417</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>4.417</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>6.083</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>23:06</t>
+        </is>
+      </c>
+      <c r="AO33" t="n">
+        <v>14.603</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.079</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0.053</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#0 M. HOWARD (Per Game)</t>
+          <t>#1 M. DIAKITE (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C34" t="n">
-        <v>15.273</v>
+        <v>9.387</v>
       </c>
       <c r="D34" t="n">
-        <v>2.091</v>
+        <v>2.581</v>
       </c>
       <c r="E34" t="n">
-        <v>3.364</v>
+        <v>3.806</v>
       </c>
       <c r="F34" t="n">
-        <v>2.455</v>
+        <v>0.806</v>
       </c>
       <c r="G34" t="n">
-        <v>7.091</v>
+        <v>2.226</v>
       </c>
       <c r="H34" t="n">
-        <v>3.727</v>
+        <v>1.806</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>2.387</v>
       </c>
       <c r="J34" t="n">
-        <v>1.545</v>
+        <v>1.226</v>
       </c>
       <c r="K34" t="n">
-        <v>0.727</v>
+        <v>3.129</v>
       </c>
       <c r="L34" t="n">
-        <v>0.182</v>
+        <v>1.452</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.323</v>
       </c>
       <c r="N34" t="n">
-        <v>0.273</v>
+        <v>1.968</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.364</v>
+        <v>1.065</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.364</v>
+        <v>1.065</v>
       </c>
       <c r="R34" t="n">
-        <v>1.818</v>
+        <v>2.613</v>
       </c>
       <c r="S34" t="n">
-        <v>2.909</v>
+        <v>1.968</v>
       </c>
       <c r="T34" t="n">
-        <v>125</v>
+        <v>389</v>
       </c>
       <c r="U34" t="n">
-        <v>2.273</v>
+        <v>1.387</v>
       </c>
       <c r="V34" t="n">
-        <v>1.545</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="W34" t="n">
-        <v>1.273</v>
+        <v>0.645</v>
       </c>
       <c r="X34" t="n">
-        <v>0.636</v>
+        <v>0.355</v>
       </c>
       <c r="Y34" t="n">
-        <v>4.727</v>
+        <v>3.581</v>
       </c>
       <c r="Z34" t="n">
-        <v>5</v>
+        <v>4.613</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.945</v>
+        <v>0.776</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.727</v>
+        <v>0.677</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.364</v>
+        <v>1.129</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.533</v>
+        <v>0.6</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.364</v>
+        <v>0.129</v>
       </c>
       <c r="AF34" t="n">
-        <v>1</v>
+        <v>0.452</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.364</v>
+        <v>0.286</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.455</v>
+        <v>0.258</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.364</v>
+        <v>0.742</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.333</v>
+        <v>0.348</v>
       </c>
       <c r="AK34" t="n">
-        <v>2</v>
+        <v>0.548</v>
       </c>
       <c r="AL34" t="n">
-        <v>5.727</v>
+        <v>1.484</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.349</v>
+        <v>0.37</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>14.578</v>
+        <v>8.147</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.552</v>
+        <v>0.628</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.625</v>
+        <v>0.663</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.048</v>
+        <v>1.152</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.162</v>
+        <v>0.131</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.357</v>
+        <v>0.299</v>
       </c>
       <c r="AU34" t="n">
-        <v>0.654</v>
+        <v>1.152</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.28</v>
+        <v>0.179</v>
       </c>
       <c r="AW34" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.034</v>
+        <v>0.167</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.058</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#1 M. DIAKITE (Per Game)</t>
+          <t>#2 K. SIMMONS (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C35" t="n">
-        <v>9.481</v>
+        <v>12.75</v>
       </c>
       <c r="D35" t="n">
-        <v>2.704</v>
+        <v>3.167</v>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>5.083</v>
       </c>
       <c r="F35" t="n">
-        <v>0.704</v>
+        <v>1.5</v>
       </c>
       <c r="G35" t="n">
-        <v>2.074</v>
+        <v>3.667</v>
       </c>
       <c r="H35" t="n">
-        <v>1.963</v>
+        <v>1.917</v>
       </c>
       <c r="I35" t="n">
-        <v>2.556</v>
+        <v>2.458</v>
       </c>
       <c r="J35" t="n">
-        <v>1.148</v>
+        <v>2.5</v>
       </c>
       <c r="K35" t="n">
-        <v>2.889</v>
+        <v>1.833</v>
       </c>
       <c r="L35" t="n">
-        <v>1.556</v>
+        <v>0.417</v>
       </c>
       <c r="M35" t="n">
-        <v>0.333</v>
+        <v>0.625</v>
       </c>
       <c r="N35" t="n">
-        <v>2.074</v>
+        <v>0.292</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.148</v>
+        <v>1.667</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.148</v>
+        <v>1.667</v>
       </c>
       <c r="R35" t="n">
-        <v>2.704</v>
+        <v>3.167</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>2.375</v>
       </c>
       <c r="T35" t="n">
-        <v>334</v>
+        <v>272</v>
       </c>
       <c r="U35" t="n">
-        <v>1.481</v>
+        <v>1.417</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>1.042</v>
       </c>
       <c r="W35" t="n">
-        <v>0.63</v>
+        <v>1.083</v>
       </c>
       <c r="X35" t="n">
-        <v>0.333</v>
+        <v>0.708</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.741</v>
+        <v>3.583</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.815</v>
+        <v>4.625</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.777</v>
+        <v>0.775</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.778</v>
+        <v>1.208</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.259</v>
+        <v>2.083</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.618</v>
+        <v>0.58</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.148</v>
+        <v>0.292</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.481</v>
+        <v>0.833</v>
       </c>
       <c r="AG35" t="n">
-        <v>0.308</v>
+        <v>0.35</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.222</v>
+        <v>0.292</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.704</v>
+        <v>0.708</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.316</v>
+        <v>0.412</v>
       </c>
       <c r="AK35" t="n">
-        <v>0.481</v>
+        <v>1.208</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.37</v>
+        <v>2.958</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.351</v>
+        <v>0.408</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>20:17</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>8.347</v>
+        <v>11.498</v>
       </c>
       <c r="AP35" t="n">
         <v>0.619</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.659</v>
+        <v>0.648</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.136</v>
+        <v>1.109</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.138</v>
+        <v>0.145</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.323</v>
+        <v>0.219</v>
       </c>
       <c r="AU35" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.184</v>
+        <v>0.231</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.09</v>
+        <v>0.022</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.156</v>
+        <v>0.089</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.041</v>
+        <v>0.093</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#2 K. SIMMONS (Per Game)</t>
+          <t>#3 M. NOWELL (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
-        <v>12.35</v>
+        <v>7</v>
       </c>
       <c r="D36" t="n">
-        <v>3.05</v>
+        <v>1.667</v>
       </c>
       <c r="E36" t="n">
-        <v>5.1</v>
+        <v>2.5</v>
       </c>
       <c r="F36" t="n">
-        <v>1.45</v>
+        <v>0.833</v>
       </c>
       <c r="G36" t="n">
-        <v>3.45</v>
+        <v>4.333</v>
       </c>
       <c r="H36" t="n">
-        <v>1.9</v>
+        <v>1.167</v>
       </c>
       <c r="I36" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>2.5</v>
       </c>
-      <c r="J36" t="n">
+      <c r="Q36" t="n">
         <v>2.5</v>
       </c>
-      <c r="K36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N36" t="n">
+      <c r="R36" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="T36" t="n">
+        <v>43</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="AM36" t="n">
         <v>0.2</v>
       </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="T36" t="n">
-        <v>210</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0.747</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0.407</v>
-      </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>11.35</v>
+        <v>10.14</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.611</v>
+        <v>0.427</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.64</v>
+        <v>0.458</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.088</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.15</v>
+        <v>0.247</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.222</v>
+        <v>0.171</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.471</v>
+        <v>1.467</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.229</v>
+        <v>0.246</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.021</v>
+        <v>0.053</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.107</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.094</v>
+        <v>0.126</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#3 M. NOWELL (Per Game)</t>
+          <t>#4 R. VILLAR (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C37" t="n">
-        <v>7</v>
+        <v>2.562</v>
       </c>
       <c r="D37" t="n">
-        <v>1.667</v>
+        <v>0.781</v>
       </c>
       <c r="E37" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="F37" t="n">
-        <v>0.833</v>
+        <v>0.156</v>
       </c>
       <c r="G37" t="n">
-        <v>4.333</v>
+        <v>0.5</v>
       </c>
       <c r="H37" t="n">
-        <v>1.167</v>
+        <v>0.531</v>
       </c>
       <c r="I37" t="n">
-        <v>1.833</v>
+        <v>0.75</v>
       </c>
       <c r="J37" t="n">
-        <v>3.667</v>
+        <v>1.312</v>
       </c>
       <c r="K37" t="n">
-        <v>1.833</v>
+        <v>1.094</v>
       </c>
       <c r="L37" t="n">
-        <v>0.833</v>
+        <v>0.438</v>
       </c>
       <c r="M37" t="n">
-        <v>0.833</v>
+        <v>0.844</v>
       </c>
       <c r="N37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T37" t="n">
+        <v>150</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>0.333</v>
       </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.167</v>
-      </c>
-      <c r="T37" t="n">
-        <v>43</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.833</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
       <c r="AK37" t="n">
-        <v>0.833</v>
+        <v>0.094</v>
       </c>
       <c r="AL37" t="n">
-        <v>4.167</v>
+        <v>0.312</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>10.14</v>
+        <v>2.611</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.427</v>
+        <v>0.58</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.458</v>
+        <v>0.616</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.981</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.247</v>
+        <v>0.203</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.171</v>
+        <v>0.304</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.467</v>
+        <v>2.471</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.245</v>
+        <v>0.093</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.053</v>
+        <v>0.041</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.108</v>
+        <v>0.094</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.128</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#4 R. VILLAR (Per Game)</t>
+          <t>#5 E. OMORUYI (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C38" t="n">
-        <v>2.714</v>
+        <v>8.042999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>0.821</v>
+        <v>2.348</v>
       </c>
       <c r="E38" t="n">
-        <v>1.25</v>
+        <v>3.522</v>
       </c>
       <c r="F38" t="n">
-        <v>0.179</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>0.464</v>
+        <v>1.696</v>
       </c>
       <c r="H38" t="n">
-        <v>0.536</v>
+        <v>1.652</v>
       </c>
       <c r="I38" t="n">
-        <v>0.786</v>
+        <v>2.217</v>
       </c>
       <c r="J38" t="n">
-        <v>1.25</v>
+        <v>1.478</v>
       </c>
       <c r="K38" t="n">
-        <v>1.107</v>
+        <v>1.609</v>
       </c>
       <c r="L38" t="n">
-        <v>0.393</v>
+        <v>0.783</v>
       </c>
       <c r="M38" t="n">
-        <v>0.75</v>
+        <v>0.826</v>
       </c>
       <c r="N38" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.826</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.087</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.087</v>
+      </c>
+      <c r="T38" t="n">
+        <v>194</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.087</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>3.391</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4.217</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.804</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.174</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>0.143</v>
       </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="T38" t="n">
-        <v>130</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.036</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.357</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.179</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AK38" t="n">
-        <v>0.107</v>
+        <v>0.522</v>
       </c>
       <c r="AL38" t="n">
-        <v>0.25</v>
+        <v>1.391</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>2.667</v>
+        <v>8.019</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.635</v>
+        <v>0.612</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.659</v>
+        <v>0.649</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.018</v>
+        <v>1.003</v>
       </c>
       <c r="AS38" t="n">
         <v>0.228</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.312</v>
+        <v>0.317</v>
       </c>
       <c r="AU38" t="n">
-        <v>2.059</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.094</v>
+        <v>0.227</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.036</v>
+        <v>0.058</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.095</v>
+        <v>0.11</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.041</v>
+        <v>0.051</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#5 E. OMORUYI (Per Game)</t>
+          <t>#6 H. DIALLO (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C39" t="n">
-        <v>7.421</v>
+        <v>12</v>
       </c>
       <c r="D39" t="n">
-        <v>2.263</v>
+        <v>4.25</v>
       </c>
       <c r="E39" t="n">
-        <v>3.316</v>
+        <v>8</v>
       </c>
       <c r="F39" t="n">
-        <v>0.474</v>
+        <v>0.375</v>
       </c>
       <c r="G39" t="n">
-        <v>1.737</v>
+        <v>1.5</v>
       </c>
       <c r="H39" t="n">
-        <v>1.474</v>
+        <v>2.375</v>
       </c>
       <c r="I39" t="n">
-        <v>2.053</v>
+        <v>3.625</v>
       </c>
       <c r="J39" t="n">
-        <v>1.474</v>
+        <v>2.125</v>
       </c>
       <c r="K39" t="n">
-        <v>1.526</v>
+        <v>4.25</v>
       </c>
       <c r="L39" t="n">
-        <v>0.737</v>
+        <v>1.125</v>
       </c>
       <c r="M39" t="n">
-        <v>0.842</v>
+        <v>1.375</v>
       </c>
       <c r="N39" t="n">
-        <v>0.316</v>
+        <v>0.75</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>1.895</v>
+        <v>1.875</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.895</v>
+        <v>1.875</v>
       </c>
       <c r="R39" t="n">
-        <v>2.263</v>
+        <v>3.25</v>
       </c>
       <c r="S39" t="n">
-        <v>2.053</v>
+        <v>3.125</v>
       </c>
       <c r="T39" t="n">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="U39" t="n">
-        <v>1.368</v>
+        <v>0.75</v>
       </c>
       <c r="V39" t="n">
         <v>1</v>
       </c>
       <c r="W39" t="n">
-        <v>0.579</v>
+        <v>2.5</v>
       </c>
       <c r="X39" t="n">
-        <v>0.316</v>
+        <v>1.625</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.211</v>
+        <v>5.25</v>
       </c>
       <c r="Z39" t="n">
-        <v>4</v>
+        <v>7.125</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.803</v>
+        <v>0.737</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.421</v>
+        <v>0.875</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.105</v>
+        <v>1.875</v>
       </c>
       <c r="AD39" t="n">
-        <v>0.381</v>
+        <v>0.467</v>
       </c>
       <c r="AE39" t="n">
-        <v>0.105</v>
+        <v>0.5</v>
       </c>
       <c r="AF39" t="n">
-        <v>0.263</v>
+        <v>2.625</v>
       </c>
       <c r="AG39" t="n">
-        <v>0.4</v>
+        <v>0.19</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.316</v>
+        <v>0.25</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>0.421</v>
+        <v>0.375</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.421</v>
+        <v>1.25</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.296</v>
+        <v>0.3</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>7.851</v>
+        <v>12.97</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.589</v>
+        <v>0.507</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.623</v>
+        <v>0.541</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.945</v>
+        <v>0.925</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.241</v>
+        <v>0.145</v>
       </c>
       <c r="AT39" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.133</v>
+      </c>
+      <c r="AV39" t="n">
         <v>0.292</v>
       </c>
-      <c r="AU39" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0.217</v>
-      </c>
       <c r="AW39" t="n">
-        <v>0.053</v>
+        <v>0.066</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.103</v>
+        <v>0.232</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.052</v>
+        <v>0.079</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#6 H. DIALLO (Per Game)</t>
+          <t>#7 R. KURUCS (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>8.5</v>
       </c>
       <c r="D40" t="n">
-        <v>4.25</v>
+        <v>1.75</v>
       </c>
       <c r="E40" t="n">
-        <v>8</v>
+        <v>3.542</v>
       </c>
       <c r="F40" t="n">
-        <v>0.375</v>
+        <v>1.25</v>
       </c>
       <c r="G40" t="n">
-        <v>1.5</v>
+        <v>2.917</v>
       </c>
       <c r="H40" t="n">
-        <v>2.375</v>
+        <v>1.25</v>
       </c>
       <c r="I40" t="n">
-        <v>3.625</v>
+        <v>1.958</v>
       </c>
       <c r="J40" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2.792</v>
+      </c>
+      <c r="S40" t="n">
         <v>2.125</v>
       </c>
-      <c r="K40" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="R40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="S40" t="n">
-        <v>3.125</v>
-      </c>
       <c r="T40" t="n">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="U40" t="n">
-        <v>0.75</v>
+        <v>0.917</v>
       </c>
       <c r="V40" t="n">
-        <v>1</v>
+        <v>0.958</v>
       </c>
       <c r="W40" t="n">
-        <v>2.5</v>
+        <v>0.958</v>
       </c>
       <c r="X40" t="n">
-        <v>1.625</v>
+        <v>0.625</v>
       </c>
       <c r="Y40" t="n">
-        <v>5.25</v>
+        <v>2.083</v>
       </c>
       <c r="Z40" t="n">
-        <v>7.125</v>
+        <v>3.208</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.737</v>
+        <v>0.649</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.875</v>
+        <v>0.792</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.875</v>
+        <v>1.667</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.467</v>
+        <v>0.475</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.5</v>
+        <v>0.125</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.625</v>
+        <v>0.625</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>0.042</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AK40" t="n">
-        <v>0.375</v>
+        <v>1.208</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.25</v>
+        <v>2.792</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.3</v>
+        <v>0.433</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>12.97</v>
+        <v>8.737</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.507</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.541</v>
+        <v>0.581</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.925</v>
+        <v>0.973</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.145</v>
+        <v>0.162</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.25</v>
+        <v>0.194</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.133</v>
+        <v>1.176</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.292</v>
+        <v>0.197</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.066</v>
+        <v>0.074</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.234</v>
+        <v>0.155</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.08</v>
+        <v>0.058</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>#7 R. KURUCS (Per Game)</t>
+          <t>#8 T. SEDEKERSKIS (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C41" t="n">
-        <v>9.1</v>
+        <v>5.364</v>
       </c>
       <c r="D41" t="n">
-        <v>1.85</v>
+        <v>1.364</v>
       </c>
       <c r="E41" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3</v>
+        <v>0.636</v>
       </c>
       <c r="G41" t="n">
-        <v>2.95</v>
+        <v>1.909</v>
       </c>
       <c r="H41" t="n">
-        <v>1.5</v>
+        <v>0.727</v>
       </c>
       <c r="I41" t="n">
-        <v>2.35</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1.7</v>
+        <v>0.909</v>
       </c>
       <c r="K41" t="n">
-        <v>2.95</v>
+        <v>2.545</v>
       </c>
       <c r="L41" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0.182</v>
       </c>
       <c r="N41" t="n">
-        <v>0.65</v>
+        <v>0.091</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.45</v>
+        <v>0.455</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.45</v>
+        <v>0.455</v>
       </c>
       <c r="R41" t="n">
-        <v>2.9</v>
+        <v>1.364</v>
       </c>
       <c r="S41" t="n">
-        <v>2.45</v>
+        <v>0.909</v>
       </c>
       <c r="T41" t="n">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="U41" t="n">
-        <v>1.1</v>
+        <v>0.182</v>
       </c>
       <c r="V41" t="n">
-        <v>0.9</v>
+        <v>0.727</v>
       </c>
       <c r="W41" t="n">
-        <v>0.9</v>
+        <v>0.364</v>
       </c>
       <c r="X41" t="n">
-        <v>0.65</v>
+        <v>0.273</v>
       </c>
       <c r="Y41" t="n">
-        <v>2.4</v>
+        <v>1.364</v>
       </c>
       <c r="Z41" t="n">
-        <v>3.7</v>
+        <v>1.818</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.649</v>
+        <v>0.75</v>
       </c>
       <c r="AB41" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AG41" t="n">
         <v>0.8</v>
       </c>
-      <c r="AC41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0.214</v>
-      </c>
       <c r="AH41" t="n">
-        <v>0.05</v>
+        <v>0.182</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.15</v>
+        <v>0.636</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.25</v>
+        <v>0.455</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.8</v>
+        <v>1.273</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.446</v>
+        <v>0.357</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>9.034000000000001</v>
+        <v>4.804</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.58</v>
+        <v>0.593</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.6</v>
+        <v>0.617</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.007</v>
+        <v>1.117</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.161</v>
+        <v>0.095</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.229</v>
+        <v>0.186</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.172</v>
+        <v>2</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.205</v>
+        <v>0.144</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.077</v>
+        <v>0.079</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.163</v>
+        <v>0.185</v>
       </c>
       <c r="AY41" t="n">
-        <v>0.061</v>
+        <v>0.031</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>#8 T. SEDEKERSKIS (Per Game)</t>
+          <t>#9 LUWAWU-CABARROT (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C42" t="n">
+        <v>17.903</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.774</v>
+      </c>
+      <c r="E42" t="n">
+        <v>5.226</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2.613</v>
+      </c>
+      <c r="G42" t="n">
+        <v>6.645</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.516</v>
+      </c>
+      <c r="I42" t="n">
+        <v>5.032</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.742</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.871</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.452</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.452</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.645</v>
+      </c>
+      <c r="T42" t="n">
+        <v>546</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.194</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.323</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="Y42" t="n">
         <v>6</v>
       </c>
-      <c r="D42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1.875</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2.375</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.375</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1</v>
-      </c>
-      <c r="T42" t="n">
-        <v>61</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.625</v>
-      </c>
       <c r="Z42" t="n">
-        <v>1.75</v>
+        <v>6.968</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.929</v>
+        <v>0.861</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.25</v>
+        <v>0.742</v>
       </c>
       <c r="AC42" t="n">
-        <v>0.5</v>
+        <v>1.645</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.5</v>
+        <v>0.451</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.375</v>
+        <v>0.548</v>
       </c>
       <c r="AF42" t="n">
-        <v>0.5</v>
+        <v>1.645</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.75</v>
+        <v>0.333</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.125</v>
+        <v>0.903</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.75</v>
+        <v>1.645</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.167</v>
+        <v>0.549</v>
       </c>
       <c r="AK42" t="n">
-        <v>0.625</v>
+        <v>1.71</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.357</v>
+        <v>0.342</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>22:22</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>5.135</v>
+        <v>15.537</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.6</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.63</v>
+        <v>0.636</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.168</v>
+        <v>1.152</v>
       </c>
       <c r="AS42" t="n">
-        <v>0.073</v>
+        <v>0.093</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.171</v>
+        <v>0.38</v>
       </c>
       <c r="AU42" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.138</v>
+        <v>0.311</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.079</v>
+        <v>0.037</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.155</v>
+        <v>0.139</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.039</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>#9 LUWAWU-CABARROT (Per Game)</t>
+          <t>#10 M. SPAGNOLO (Per Game)</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C43" t="n">
-        <v>17.556</v>
+        <v>7.484</v>
       </c>
       <c r="D43" t="n">
-        <v>2.704</v>
+        <v>2.226</v>
       </c>
       <c r="E43" t="n">
-        <v>5.185</v>
+        <v>4.387</v>
       </c>
       <c r="F43" t="n">
-        <v>2.593</v>
+        <v>0.484</v>
       </c>
       <c r="G43" t="n">
-        <v>6.444</v>
+        <v>1.387</v>
       </c>
       <c r="H43" t="n">
-        <v>4.37</v>
+        <v>1.581</v>
       </c>
       <c r="I43" t="n">
-        <v>4.815</v>
+        <v>1.871</v>
       </c>
       <c r="J43" t="n">
-        <v>1.815</v>
+        <v>2.065</v>
       </c>
       <c r="K43" t="n">
-        <v>3.037</v>
+        <v>2.129</v>
       </c>
       <c r="L43" t="n">
-        <v>0.741</v>
+        <v>0.419</v>
       </c>
       <c r="M43" t="n">
-        <v>0.963</v>
+        <v>0.871</v>
       </c>
       <c r="N43" t="n">
-        <v>0.444</v>
+        <v>0.645</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.519</v>
+        <v>1.065</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.519</v>
+        <v>1.065</v>
       </c>
       <c r="R43" t="n">
-        <v>2.37</v>
+        <v>1.645</v>
       </c>
       <c r="S43" t="n">
-        <v>3.481</v>
+        <v>2.226</v>
       </c>
       <c r="T43" t="n">
-        <v>469</v>
+        <v>303</v>
       </c>
       <c r="U43" t="n">
-        <v>2.074</v>
+        <v>1.484</v>
       </c>
       <c r="V43" t="n">
-        <v>2.037</v>
+        <v>0.774</v>
       </c>
       <c r="W43" t="n">
-        <v>1.407</v>
+        <v>0.871</v>
       </c>
       <c r="X43" t="n">
-        <v>0.889</v>
+        <v>0.548</v>
       </c>
       <c r="Y43" t="n">
-        <v>5.778</v>
+        <v>2.516</v>
       </c>
       <c r="Z43" t="n">
-        <v>6.667</v>
+        <v>3.129</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.867</v>
+        <v>0.804</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.704</v>
+        <v>0.774</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.593</v>
+        <v>1.774</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.442</v>
+        <v>0.436</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.593</v>
+        <v>0.516</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.741</v>
+        <v>1.355</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.34</v>
+        <v>0.381</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.037</v>
+        <v>0.097</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.704</v>
+        <v>0.419</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.609</v>
+        <v>0.231</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.556</v>
+        <v>0.387</v>
       </c>
       <c r="AL43" t="n">
-        <v>4.741</v>
+        <v>0.968</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.328</v>
+        <v>0.4</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>15.267</v>
+        <v>7.662</v>
       </c>
       <c r="AP43" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="AQ43" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="AQ43" t="n">
-        <v>0.638</v>
-      </c>
       <c r="AR43" t="n">
-        <v>1.15</v>
+        <v>0.977</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.099</v>
+        <v>0.139</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.376</v>
+        <v>0.274</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.195</v>
+        <v>1.939</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.307</v>
+        <v>0.176</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.039</v>
+        <v>0.025</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.149</v>
+        <v>0.118</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>#10 M. SPAGNOLO (Per Game)</t>
+          <t>#11 T. FORREST (Per Game)</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C44" t="n">
-        <v>7.296</v>
+        <v>14.429</v>
       </c>
       <c r="D44" t="n">
-        <v>2.259</v>
+        <v>3.19</v>
       </c>
       <c r="E44" t="n">
-        <v>4.667</v>
+        <v>5.19</v>
       </c>
       <c r="F44" t="n">
-        <v>0.407</v>
+        <v>0.857</v>
       </c>
       <c r="G44" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" t="n">
+        <v>5.476</v>
+      </c>
+      <c r="I44" t="n">
+        <v>5.952</v>
+      </c>
+      <c r="J44" t="n">
+        <v>4</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.048</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.429</v>
+      </c>
+      <c r="S44" t="n">
+        <v>4.619</v>
+      </c>
+      <c r="T44" t="n">
+        <v>429</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2.571</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.571</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.333</v>
       </c>
-      <c r="H44" t="n">
-        <v>1.556</v>
-      </c>
-      <c r="I44" t="n">
-        <v>1.889</v>
-      </c>
-      <c r="J44" t="n">
-        <v>2.037</v>
-      </c>
-      <c r="K44" t="n">
-        <v>2.111</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1.111</v>
-      </c>
-      <c r="R44" t="n">
-        <v>1.593</v>
-      </c>
-      <c r="S44" t="n">
-        <v>2.148</v>
-      </c>
-      <c r="T44" t="n">
-        <v>249</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.481</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0.889</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0.852</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>2.481</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>3.148</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.788</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0.741</v>
-      </c>
       <c r="AC44" t="n">
-        <v>1.852</v>
+        <v>2.524</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.4</v>
+        <v>0.528</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.593</v>
+        <v>0.333</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.556</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.381</v>
+        <v>0.412</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.111</v>
+        <v>0.143</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.481</v>
+        <v>0.762</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.231</v>
+        <v>0.188</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.296</v>
+        <v>0.714</v>
       </c>
       <c r="AL44" t="n">
-        <v>0.852</v>
+        <v>2.238</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.348</v>
+        <v>0.319</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>19:47</t>
+          <t>25:26</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>7.942</v>
+        <v>12.81</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.478</v>
+        <v>0.547</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.534</v>
+        <v>0.667</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.919</v>
+        <v>1.126</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.14</v>
+        <v>0.156</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.259</v>
+        <v>0.669</v>
       </c>
       <c r="AU44" t="n">
-        <v>1.833</v>
+        <v>2</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.18</v>
+        <v>0.226</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.028</v>
+        <v>0.022</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.117</v>
+        <v>0.13</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.145</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>#11 T. FORREST (Per Game)</t>
+          <t>#14 J. EDWARDS (Per Game)</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C45" t="n">
-        <v>14.333</v>
+        <v>4.833</v>
       </c>
       <c r="D45" t="n">
-        <v>3.056</v>
+        <v>1.667</v>
       </c>
       <c r="E45" t="n">
-        <v>5.167</v>
+        <v>3.083</v>
       </c>
       <c r="F45" t="n">
-        <v>0.889</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>2.944</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>5.556</v>
+        <v>1.5</v>
       </c>
       <c r="I45" t="n">
-        <v>6</v>
+        <v>2.833</v>
       </c>
       <c r="J45" t="n">
-        <v>4.111</v>
+        <v>0.25</v>
       </c>
       <c r="K45" t="n">
-        <v>2.889</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
+        <v>1.583</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.083</v>
+      </c>
+      <c r="T45" t="n">
+        <v>76</v>
+      </c>
+      <c r="U45" t="n">
         <v>0.5</v>
       </c>
-      <c r="M45" t="n">
+      <c r="V45" t="n">
         <v>1.167</v>
       </c>
-      <c r="N45" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1.944</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>1.944</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="S45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T45" t="n">
-        <v>364</v>
-      </c>
-      <c r="U45" t="n">
-        <v>2.444</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.556</v>
-      </c>
       <c r="W45" t="n">
-        <v>0.722</v>
+        <v>0.167</v>
       </c>
       <c r="X45" t="n">
-        <v>0.556</v>
+        <v>0.083</v>
       </c>
       <c r="Y45" t="n">
-        <v>7</v>
+        <v>2.833</v>
       </c>
       <c r="Z45" t="n">
-        <v>7.833</v>
+        <v>4.583</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.894</v>
+        <v>0.618</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.278</v>
+        <v>0.167</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.667</v>
+        <v>0.833</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.479</v>
+        <v>0.2</v>
       </c>
       <c r="AE45" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG45" t="n">
         <v>0.333</v>
       </c>
-      <c r="AF45" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0.5</v>
-      </c>
       <c r="AH45" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.278</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>0.341</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>25:35</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>12.696</v>
+        <v>5.163</v>
       </c>
       <c r="AP45" t="n">
         <v>0.541</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.667</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.129</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.153</v>
+        <v>0.161</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.486</v>
       </c>
       <c r="AU45" t="n">
-        <v>2.114</v>
+        <v>0.3</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.222</v>
+        <v>0.187</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.023</v>
+        <v>0.15</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.123</v>
+        <v>0.175</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.151</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>#14 J. EDWARDS (Per Game)</t>
+          <t>#17 G. RADZEVICIUS (Per Game)</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C46" t="n">
-        <v>4.25</v>
+        <v>5.091</v>
       </c>
       <c r="D46" t="n">
-        <v>1.375</v>
+        <v>1.091</v>
       </c>
       <c r="E46" t="n">
-        <v>2.625</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>0.864</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1.909</v>
       </c>
       <c r="H46" t="n">
-        <v>1.5</v>
+        <v>0.318</v>
       </c>
       <c r="I46" t="n">
-        <v>2.875</v>
+        <v>0.545</v>
       </c>
       <c r="J46" t="n">
-        <v>0.125</v>
+        <v>1.273</v>
       </c>
       <c r="K46" t="n">
-        <v>1.625</v>
+        <v>2.318</v>
       </c>
       <c r="L46" t="n">
-        <v>0.875</v>
+        <v>1.182</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>0.591</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0.182</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.625</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.625</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="R46" t="n">
-        <v>2.25</v>
+        <v>1.409</v>
       </c>
       <c r="S46" t="n">
-        <v>2.25</v>
+        <v>0.864</v>
       </c>
       <c r="T46" t="n">
-        <v>37</v>
+        <v>159</v>
       </c>
       <c r="U46" t="n">
         <v>0.5</v>
       </c>
       <c r="V46" t="n">
-        <v>0.75</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="W46" t="n">
-        <v>0.25</v>
+        <v>0.318</v>
       </c>
       <c r="X46" t="n">
-        <v>0.125</v>
+        <v>0.182</v>
       </c>
       <c r="Y46" t="n">
-        <v>2.625</v>
+        <v>0.727</v>
       </c>
       <c r="Z46" t="n">
-        <v>4.5</v>
+        <v>1.136</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.583</v>
+        <v>0.64</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.25</v>
+        <v>0.409</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.875</v>
+        <v>0.591</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.286</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.125</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>0.727</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>0.591</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.182</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>4.515</v>
+        <v>4.831</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.524</v>
+        <v>0.61</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.546</v>
+        <v>0.613</v>
       </c>
       <c r="AR46" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.054</v>
       </c>
       <c r="AS46" t="n">
-        <v>0.138</v>
+        <v>0.141</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.571</v>
+        <v>0.081</v>
       </c>
       <c r="AU46" t="n">
-        <v>0.2</v>
+        <v>1.867</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.173</v>
+        <v>0.11</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.152</v>
+        <v>0.128</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.004</v>
+        <v>0.043</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>#17 G. RADZEVICIUS (Per Game)</t>
+          <t>#18 K. DIOP (Per Game)</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C47" t="n">
-        <v>5.389</v>
+        <v>3.526</v>
       </c>
       <c r="D47" t="n">
-        <v>1.111</v>
+        <v>1.211</v>
       </c>
       <c r="E47" t="n">
-        <v>2.167</v>
+        <v>1.842</v>
       </c>
       <c r="F47" t="n">
-        <v>0.944</v>
+        <v>0.053</v>
       </c>
       <c r="G47" t="n">
-        <v>2.111</v>
+        <v>0.105</v>
       </c>
       <c r="H47" t="n">
-        <v>0.333</v>
+        <v>0.947</v>
       </c>
       <c r="I47" t="n">
-        <v>0.556</v>
+        <v>1.316</v>
       </c>
       <c r="J47" t="n">
-        <v>1.333</v>
+        <v>0.895</v>
       </c>
       <c r="K47" t="n">
-        <v>2.611</v>
+        <v>3.105</v>
       </c>
       <c r="L47" t="n">
-        <v>1.389</v>
+        <v>1.211</v>
       </c>
       <c r="M47" t="n">
-        <v>0.667</v>
+        <v>0.579</v>
       </c>
       <c r="N47" t="n">
-        <v>0.222</v>
+        <v>1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>0.778</v>
+        <v>1.053</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.778</v>
+        <v>1.053</v>
       </c>
       <c r="R47" t="n">
-        <v>1.389</v>
+        <v>2.158</v>
       </c>
       <c r="S47" t="n">
-        <v>0.944</v>
+        <v>1.368</v>
       </c>
       <c r="T47" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="U47" t="n">
-        <v>0.444</v>
+        <v>0.316</v>
       </c>
       <c r="V47" t="n">
-        <v>0.722</v>
+        <v>0.211</v>
       </c>
       <c r="W47" t="n">
-        <v>0.278</v>
+        <v>0.211</v>
       </c>
       <c r="X47" t="n">
-        <v>0.167</v>
+        <v>0.158</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.778</v>
+        <v>1.737</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.222</v>
+        <v>2.316</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.636</v>
+        <v>0.75</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.444</v>
+        <v>0.316</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.611</v>
+        <v>0.579</v>
       </c>
       <c r="AD47" t="n">
-        <v>0.727</v>
+        <v>0.545</v>
       </c>
       <c r="AE47" t="n">
-        <v>0.222</v>
+        <v>0.105</v>
       </c>
       <c r="AF47" t="n">
-        <v>0.889</v>
+        <v>0.263</v>
       </c>
       <c r="AG47" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.278</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>0.722</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0.385</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>0.667</v>
+        <v>0.053</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.389</v>
+        <v>0.105</v>
       </c>
       <c r="AM47" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AO47" t="n">
-        <v>5.3</v>
+        <v>3.579</v>
       </c>
       <c r="AP47" t="n">
-        <v>0.591</v>
+        <v>0.662</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.596</v>
+        <v>0.698</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.017</v>
+        <v>0.985</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.147</v>
+        <v>0.294</v>
       </c>
       <c r="AT47" t="n">
-        <v>0.078</v>
+        <v>0.486</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.714</v>
+        <v>0.85</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.117</v>
+        <v>0.1</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.08</v>
+        <v>0.089</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.141</v>
+        <v>0.211</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.046</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>#18 K. DIOP (Per Game)</t>
+          <t>#21 J. BOL (Per Game)</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="C48" t="n">
-        <v>3.526</v>
+        <v>0.667</v>
       </c>
       <c r="D48" t="n">
-        <v>1.211</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1.842</v>
+        <v>0.667</v>
       </c>
       <c r="F48" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.105</v>
+        <v>0.333</v>
       </c>
       <c r="H48" t="n">
-        <v>0.947</v>
+        <v>0.667</v>
       </c>
       <c r="I48" t="n">
-        <v>1.316</v>
+        <v>0.667</v>
       </c>
       <c r="J48" t="n">
-        <v>0.895</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>3.105</v>
+        <v>0.333</v>
       </c>
       <c r="L48" t="n">
-        <v>1.211</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.579</v>
+        <v>0.333</v>
       </c>
       <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="T48" t="n">
         <v>1</v>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>1.053</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>1.053</v>
-      </c>
-      <c r="R48" t="n">
-        <v>2.158</v>
-      </c>
-      <c r="S48" t="n">
-        <v>1.368</v>
-      </c>
-      <c r="T48" t="n">
-        <v>141</v>
-      </c>
       <c r="U48" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0.158</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.737</v>
+        <v>0.667</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.316</v>
+        <v>0.667</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.316</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.579</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>0.545</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>0.263</v>
+        <v>0.667</v>
       </c>
       <c r="AG48" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
         <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AJ48" t="n">
         <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>0.053</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>0.105</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>01:47</t>
         </is>
       </c>
       <c r="AO48" t="n">
-        <v>3.579</v>
+        <v>1.293</v>
       </c>
       <c r="AP48" t="n">
-        <v>0.662</v>
+        <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.698</v>
+        <v>0.258</v>
       </c>
       <c r="AR48" t="n">
-        <v>0.985</v>
+        <v>0.515</v>
       </c>
       <c r="AS48" t="n">
-        <v>0.294</v>
+        <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>0.486</v>
+        <v>0.667</v>
       </c>
       <c r="AU48" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.1</v>
+        <v>0.325</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.212</v>
+        <v>0.203</v>
       </c>
       <c r="AY48" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>#21 J. BOL (Per Game)</t>
+          <t>#25 C. FRISCH (Per Game)</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C49" t="n">
-        <v>0.667</v>
+        <v>4.188</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="E49" t="n">
-        <v>0.667</v>
+        <v>1.594</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="G49" t="n">
-        <v>0.333</v>
+        <v>2.281</v>
       </c>
       <c r="H49" t="n">
-        <v>0.667</v>
+        <v>0.312</v>
       </c>
       <c r="I49" t="n">
-        <v>0.667</v>
+        <v>0.375</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="K49" t="n">
-        <v>0.333</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>0.844</v>
       </c>
       <c r="M49" t="n">
-        <v>0.333</v>
+        <v>0.406</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>0.188</v>
       </c>
       <c r="R49" t="n">
-        <v>0.333</v>
+        <v>1.312</v>
       </c>
       <c r="S49" t="n">
-        <v>0.333</v>
+        <v>0.406</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>146</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.667</v>
+        <v>0.594</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.667</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="AA49" t="n">
-        <v>1</v>
+        <v>0.731</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>0.281</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.667</v>
+        <v>0.531</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.333</v>
+        <v>0.719</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>0.522</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>1.562</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>01:47</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>1.293</v>
+        <v>4.228</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.258</v>
+        <v>0.518</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.515</v>
+        <v>0.991</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>0.044</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.667</v>
+        <v>0.081</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.325</v>
+        <v>0.146</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>0.076</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.204</v>
+        <v>0.167</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>#25 C. FRISCH (Per Game)</t>
+          <t>#30 M. KHATIASHVILI (Per Game)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>0.714</v>
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.714</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0.929</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="H50" t="n">
-        <v>0.286</v>
+        <v>2</v>
       </c>
       <c r="I50" t="n">
-        <v>0.357</v>
+        <v>2</v>
       </c>
       <c r="J50" t="n">
-        <v>0.357</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>2.143</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.929</v>
+        <v>0.5</v>
       </c>
       <c r="M50" t="n">
-        <v>0.464</v>
+        <v>0.5</v>
       </c>
       <c r="N50" t="n">
-        <v>0.286</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.357</v>
+        <v>0.5</v>
       </c>
       <c r="S50" t="n">
-        <v>0.393</v>
+        <v>1.5</v>
       </c>
       <c r="T50" t="n">
-        <v>136</v>
+        <v>11</v>
       </c>
       <c r="U50" t="n">
-        <v>0.571</v>
+        <v>1</v>
       </c>
       <c r="V50" t="n">
-        <v>1.071</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0.143</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0.07099999999999999</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.607</v>
+        <v>2</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.821</v>
+        <v>2</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.739</v>
+        <v>1</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.321</v>
+        <v>0.5</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.714</v>
+        <v>0.5</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="AE50" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AF50" t="n">
-        <v>0.536</v>
+        <v>0.5</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.133</v>
+        <v>1</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.393</v>
+        <v>0</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.524</v>
+        <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>0.536</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>0.306</v>
+        <v>0</v>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>05:02</t>
         </is>
       </c>
       <c r="AO50" t="n">
-        <v>4.586</v>
+        <v>2.38</v>
       </c>
       <c r="AP50" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.515</v>
+        <v>0.84</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.981</v>
+        <v>1.681</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.047</v>
+        <v>0</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.068</v>
+        <v>1.333</v>
       </c>
       <c r="AU50" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.151</v>
+        <v>0.212</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.08</v>
+        <v>0.116</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.172</v>
+        <v>0</v>
       </c>
       <c r="AY50" t="n">
-        <v>0.012</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>#30 M. KHATIASHVILI (Per Game)</t>
+          <t>#33 V. HRABAR (Per Game)</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
@@ -8202,16 +8202,16 @@
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="S51" t="n">
-        <v>1.5</v>
+        <v>0.2</v>
       </c>
       <c r="T51" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
@@ -8223,37 +8223,37 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="Z51" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="AA51" t="n">
         <v>1</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="n">
         <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AJ51" t="n">
         <v>0</v>
@@ -8269,38 +8269,38 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>05:02</t>
+          <t>01:48</t>
         </is>
       </c>
       <c r="AO51" t="n">
-        <v>2.38</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AP51" t="n">
         <v>0.667</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.84</v>
+        <v>0.727</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.681</v>
+        <v>1.453</v>
       </c>
       <c r="AS51" t="n">
         <v>0</v>
       </c>
       <c r="AT51" t="n">
-        <v>1.333</v>
+        <v>0.333</v>
       </c>
       <c r="AU51" t="n">
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.212</v>
+        <v>0.17</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.116</v>
+        <v>0.129</v>
       </c>
       <c r="AX51" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AY51" t="n">
         <v>0</v>
@@ -8309,404 +8309,404 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>#33 V. HRABAR (Per Game)</t>
+          <t>#77 S. JOKSIMOVIC (Per Game)</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C52" t="n">
-        <v>0.75</v>
+        <v>1.933</v>
       </c>
       <c r="D52" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="E52" t="n">
-        <v>0.25</v>
+        <v>0.667</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G52" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="I52" t="n">
-        <v>0.25</v>
+        <v>0.533</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="K52" t="n">
-        <v>0.25</v>
+        <v>0.467</v>
       </c>
       <c r="L52" t="n">
-        <v>0.25</v>
+        <v>0.267</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>0.533</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>0.533</v>
       </c>
       <c r="R52" t="n">
-        <v>0.75</v>
+        <v>0.733</v>
       </c>
       <c r="S52" t="n">
-        <v>0.25</v>
+        <v>0.533</v>
       </c>
       <c r="T52" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>0.067</v>
       </c>
       <c r="Y52" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0.462</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AD52" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z52" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
       <c r="AE52" t="n">
         <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.25</v>
+        <v>0.333</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AL52" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>01:54</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AO52" t="n">
-        <v>0.61</v>
+        <v>2.435</v>
       </c>
       <c r="AP52" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.615</v>
+        <v>0.508</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.23</v>
+        <v>0.794</v>
       </c>
       <c r="AS52" t="n">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="AT52" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>1.125</v>
       </c>
       <c r="AV52" t="n">
-        <v>0.143</v>
+        <v>0.198</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.153</v>
+        <v>0.057</v>
       </c>
       <c r="AX52" t="n">
-        <v>0.143</v>
+        <v>0.092</v>
       </c>
       <c r="AY52" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>#77 S. JOKSIMOVIC (Per Game)</t>
+          <t>#99 L. SAMANIC (Per Game)</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>1.933</v>
+        <v>19</v>
       </c>
       <c r="D53" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>5</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4</v>
+      </c>
+      <c r="H53" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I53" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2</v>
+      </c>
+      <c r="S53" t="n">
+        <v>6</v>
+      </c>
+      <c r="T53" t="n">
+        <v>49</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>23:04</t>
+        </is>
+      </c>
+      <c r="AO53" t="n">
+        <v>13.74</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>1.383</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV53" t="n">
         <v>0.267</v>
       </c>
-      <c r="E53" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="T53" t="n">
-        <v>23</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="X53" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="AO53" t="n">
-        <v>2.435</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>0.508</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>0.198</v>
-      </c>
       <c r="AW53" t="n">
-        <v>0.057</v>
+        <v>0.051</v>
       </c>
       <c r="AX53" t="n">
-        <v>0.093</v>
+        <v>0.141</v>
       </c>
       <c r="AY53" t="n">
-        <v>0.02</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>#99 L. SAMANIC (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C54" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>1.469</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="M54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>1</v>
+        <v>0.656</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="U54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.846</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
         <v>0</v>
@@ -8721,7 +8721,7 @@
         <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -8736,207 +8736,207 @@
         <v>0</v>
       </c>
       <c r="AK54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>0.375</v>
+        <v>0</v>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO54" t="n">
-        <v>13.74</v>
+        <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>0.639</v>
+        <v>0</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.746</v>
+        <v>0</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.383</v>
+        <v>0</v>
       </c>
       <c r="AS54" t="n">
-        <v>0.073</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.267</v>
+        <v>0</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="AX54" t="n">
-        <v>0.142</v>
+        <v>0</v>
       </c>
       <c r="AY54" t="n">
-        <v>0.038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>93.65600000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>21.375</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>37.031</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>10.25</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>27.656</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>20.156</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>25.188</v>
       </c>
       <c r="J55" t="n">
-        <v>0</v>
+        <v>17.281</v>
       </c>
       <c r="K55" t="n">
-        <v>1.571</v>
+        <v>26.281</v>
       </c>
       <c r="L55" t="n">
-        <v>1.179</v>
+        <v>10.375</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>7.812</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0.714</v>
+        <v>13.469</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>12.812</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>21.969</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>22.656</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>3553</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>12.469</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>10.719</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>4.656</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>32.094</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>40.406</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>0.794</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>6.781</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>13.469</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>0.503</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.656</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>8.343999999999999</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>0.318</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>2.531</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>6.531</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>0.388</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>7.719</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>21.125</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>0.365</v>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>89.239</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>0.618</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>0.151</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>1.283</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AY55" t="n">
         <v>0</v>
@@ -8945,477 +8945,159 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>86.812</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>22.875</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>42.219</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>8.156000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>25.031</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>16.594</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>21.375</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>16.719</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>23.75</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>10.594</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>6.719</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>6.406</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>12.906</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>11.969</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>21.938</v>
       </c>
       <c r="T56" t="n">
-        <v>57</v>
+        <v>3073</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>10.531</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>10.719</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>5.625</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>3.344</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>27.688</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>35.469</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>0.781</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>7.469</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>16.125</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>0.463</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>4.312</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>0.359</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.312</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>3.188</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>0.412</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>6.844</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>21.844</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO56" t="n">
-        <v>0.714</v>
+        <v>89.56100000000001</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>0.522</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>0.969</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>0.144</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>0.247</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>1.295</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>0.201</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>0.129</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>28</v>
-      </c>
-      <c r="C57" t="n">
-        <v>92.464</v>
-      </c>
-      <c r="D57" t="n">
-        <v>21.179</v>
-      </c>
-      <c r="E57" t="n">
-        <v>37.071</v>
-      </c>
-      <c r="F57" t="n">
-        <v>9.964</v>
-      </c>
-      <c r="G57" t="n">
-        <v>27.321</v>
-      </c>
-      <c r="H57" t="n">
-        <v>20.214</v>
-      </c>
-      <c r="I57" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="J57" t="n">
-        <v>17.286</v>
-      </c>
-      <c r="K57" t="n">
-        <v>26.143</v>
-      </c>
-      <c r="L57" t="n">
-        <v>10.357</v>
-      </c>
-      <c r="M57" t="n">
-        <v>7.714</v>
-      </c>
-      <c r="N57" t="n">
-        <v>6.393</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
-        <v>13.821</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>13.107</v>
-      </c>
-      <c r="R57" t="n">
-        <v>22.25</v>
-      </c>
-      <c r="S57" t="n">
-        <v>22.679</v>
-      </c>
-      <c r="T57" t="n">
-        <v>3043</v>
-      </c>
-      <c r="U57" t="n">
-        <v>12.214</v>
-      </c>
-      <c r="V57" t="n">
-        <v>10.821</v>
-      </c>
-      <c r="W57" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="X57" t="n">
-        <v>4.607</v>
-      </c>
-      <c r="Y57" t="n">
-        <v>32.036</v>
-      </c>
-      <c r="Z57" t="n">
-        <v>40.429</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>6.643</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>13.429</v>
-      </c>
-      <c r="AD57" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>2.714</v>
-      </c>
-      <c r="AF57" t="n">
-        <v>8.464</v>
-      </c>
-      <c r="AG57" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="AH57" t="n">
-        <v>2.679</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>6.643</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>7.286</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>20.679</v>
-      </c>
-      <c r="AM57" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO57" t="n">
-        <v>89.324</v>
-      </c>
-      <c r="AP57" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0.612</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>1.035</v>
-      </c>
-      <c r="AS57" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="AT57" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>1.251</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AX57" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AY57" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>28</v>
-      </c>
-      <c r="C58" t="n">
-        <v>87.25</v>
-      </c>
-      <c r="D58" t="n">
-        <v>22.464</v>
-      </c>
-      <c r="E58" t="n">
-        <v>41.964</v>
-      </c>
-      <c r="F58" t="n">
-        <v>8.393000000000001</v>
-      </c>
-      <c r="G58" t="n">
-        <v>24.857</v>
-      </c>
-      <c r="H58" t="n">
-        <v>17.143</v>
-      </c>
-      <c r="I58" t="n">
-        <v>21.964</v>
-      </c>
-      <c r="J58" t="n">
-        <v>16.786</v>
-      </c>
-      <c r="K58" t="n">
-        <v>23.893</v>
-      </c>
-      <c r="L58" t="n">
-        <v>10.429</v>
-      </c>
-      <c r="M58" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="N58" t="n">
-        <v>6.429</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>12.857</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>11.929</v>
-      </c>
-      <c r="R58" t="n">
-        <v>23.036</v>
-      </c>
-      <c r="S58" t="n">
-        <v>22.214</v>
-      </c>
-      <c r="T58" t="n">
-        <v>2718</v>
-      </c>
-      <c r="U58" t="n">
-        <v>10.857</v>
-      </c>
-      <c r="V58" t="n">
-        <v>10.714</v>
-      </c>
-      <c r="W58" t="n">
-        <v>5.357</v>
-      </c>
-      <c r="X58" t="n">
-        <v>3.214</v>
-      </c>
-      <c r="Y58" t="n">
-        <v>28.393</v>
-      </c>
-      <c r="Z58" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>6.929</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>15.321</v>
-      </c>
-      <c r="AD58" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="AE58" t="n">
-        <v>4.286</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>12.107</v>
-      </c>
-      <c r="AG58" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="AH58" t="n">
-        <v>1.429</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>3.321</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AK58" t="n">
-        <v>6.964</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>21.536</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO58" t="n">
-        <v>89.343</v>
-      </c>
-      <c r="AP58" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>0.977</v>
-      </c>
-      <c r="AS58" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="AT58" t="n">
-        <v>0.257</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>1.306</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="AX58" t="n">
-        <v>0.131</v>
-      </c>
-      <c r="AY58" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Baskonia.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/aggregate/AGGREGATE_Baskonia.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2523.64</v>
+        <v>2677.08</v>
       </c>
       <c r="C2" t="n">
-        <v>2525.3</v>
+        <v>2680.82</v>
       </c>
       <c r="D2" t="n">
-        <v>118.6789688353859</v>
+        <v>118.508516051059</v>
       </c>
       <c r="E2" t="n">
-        <v>110.0067318734408</v>
+        <v>110.0409576174454</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5681159420289855</v>
+        <v>0.5690443529949702</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1509293888585396</v>
+        <v>0.1507081627515667</v>
       </c>
       <c r="H2" t="n">
-        <v>0.304029304029304</v>
+        <v>0.2973913043478261</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3115942028985507</v>
+        <v>0.314586191129401</v>
       </c>
       <c r="J2" t="n">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="K2" t="n">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="L2" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="M2" t="n">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="N2" t="n">
-        <v>1027</v>
+        <v>1091</v>
       </c>
       <c r="O2" t="n">
-        <v>1293</v>
+        <v>1368</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6246376811594203</v>
+        <v>0.6255144032921811</v>
       </c>
       <c r="Q2" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="R2" t="n">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2082125603864734</v>
+        <v>0.2062185642432556</v>
       </c>
       <c r="T2" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="U2" t="n">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1289855072463768</v>
+        <v>0.1312299954275263</v>
       </c>
       <c r="W2" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="X2" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1009661835748792</v>
+        <v>0.1024234110653864</v>
       </c>
       <c r="Z2" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AA2" t="n">
-        <v>676</v>
+        <v>714</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3265700483091787</v>
+        <v>0.326474622770919</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.794276875483372</v>
+        <v>0.797514619883041</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5034802784222738</v>
+        <v>0.4988913525498891</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3183520599250936</v>
+        <v>0.3240418118466899</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.3875598086124402</v>
+        <v>0.3883928571428572</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.3653846153846154</v>
+        <v>0.3669467787114846</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.588553750966744</v>
+        <v>1.595029239766082</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.6367041198501873</v>
+        <v>0.6480836236933798</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.111864406779661</v>
+        <v>1.116204690831557</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.9661016949152542</v>
+        <v>0.9636363636363636</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.033132530120482</v>
+        <v>1.04093567251462</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.610738255033557</v>
+        <v>1.607594936708861</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.283062645011601</v>
+        <v>1.283516483516484</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.802784222737819</v>
+        <v>4.806593406593406</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.08584686774942</v>
+        <v>6.09010989010989</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.86375</v>
+        <v>78.73764705882353</v>
       </c>
       <c r="C3" t="n">
-        <v>78.91562500000001</v>
+        <v>78.84764705882354</v>
       </c>
       <c r="D3" t="n">
-        <v>118.6789688353859</v>
+        <v>118.508516051059</v>
       </c>
       <c r="E3" t="n">
-        <v>110.0067318734408</v>
+        <v>110.0409576174454</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5681159420289855</v>
+        <v>0.5690443529949704</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1509293888585396</v>
+        <v>0.1507081627515667</v>
       </c>
       <c r="H3" t="n">
-        <v>0.304029304029304</v>
+        <v>0.2973913043478261</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3115942028985507</v>
+        <v>0.3145861911294009</v>
       </c>
       <c r="J3" t="n">
-        <v>12.46875</v>
+        <v>12.47058823529412</v>
       </c>
       <c r="K3" t="n">
-        <v>10.71875</v>
+        <v>10.47058823529412</v>
       </c>
       <c r="L3" t="n">
-        <v>7.5</v>
+        <v>7.470588235294118</v>
       </c>
       <c r="M3" t="n">
-        <v>12.8125</v>
+        <v>12.70588235294118</v>
       </c>
       <c r="N3" t="n">
-        <v>32.09375</v>
+        <v>32.08823529411764</v>
       </c>
       <c r="O3" t="n">
-        <v>40.40625</v>
+        <v>40.23529411764706</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6246376811594203</v>
+        <v>0.625514403292181</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.78125</v>
+        <v>6.617647058823529</v>
       </c>
       <c r="R3" t="n">
-        <v>13.46875</v>
+        <v>13.26470588235294</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2082125603864734</v>
+        <v>0.2062185642432556</v>
       </c>
       <c r="T3" t="n">
-        <v>2.65625</v>
+        <v>2.735294117647059</v>
       </c>
       <c r="U3" t="n">
-        <v>8.34375</v>
+        <v>8.441176470588236</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1289855072463768</v>
+        <v>0.1312299954275263</v>
       </c>
       <c r="W3" t="n">
-        <v>2.53125</v>
+        <v>2.558823529411764</v>
       </c>
       <c r="X3" t="n">
-        <v>6.53125</v>
+        <v>6.588235294117647</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1009661835748792</v>
+        <v>0.1024234110653864</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.71875</v>
+        <v>7.705882352941177</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.125</v>
+        <v>21</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3265700483091787</v>
+        <v>0.326474622770919</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.794276875483372</v>
+        <v>0.797514619883041</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5034802784222738</v>
+        <v>0.4988913525498891</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3183520599250936</v>
+        <v>0.3240418118466899</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.3875598086124402</v>
+        <v>0.3883928571428572</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.3653846153846154</v>
+        <v>0.3669467787114846</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.588553750966744</v>
+        <v>1.595029239766082</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.6367041198501873</v>
+        <v>0.6480836236933798</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.111864406779661</v>
+        <v>1.116204690831557</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.9661016949152542</v>
+        <v>0.9636363636363636</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.033132530120482</v>
+        <v>1.04093567251462</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.610738255033557</v>
+        <v>1.607594936708861</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.283062645011601</v>
+        <v>1.283516483516483</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.802784222737819</v>
+        <v>4.806593406593406</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.08584686774942</v>
+        <v>6.09010989010989</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2526.959999999999</v>
+        <v>2684.559999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>2525.3</v>
+        <v>2680.82</v>
       </c>
       <c r="D4" t="n">
-        <v>110.0067318734408</v>
+        <v>110.0409576174454</v>
       </c>
       <c r="E4" t="n">
-        <v>118.6789688353859</v>
+        <v>118.508516051059</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5220724907063197</v>
+        <v>0.5211421098517872</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1441052910717526</v>
+        <v>0.1441413108997039</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2872881355932204</v>
+        <v>0.2913697545526524</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2467472118959108</v>
+        <v>0.2436791630340018</v>
       </c>
       <c r="J4" t="n">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="K4" t="n">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="L4" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="M4" t="n">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="N4" t="n">
-        <v>886</v>
+        <v>932</v>
       </c>
       <c r="O4" t="n">
-        <v>1135</v>
+        <v>1197</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5274163568773235</v>
+        <v>0.5217959895379251</v>
       </c>
       <c r="Q4" t="n">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="R4" t="n">
-        <v>516</v>
+        <v>562</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2397769516728624</v>
+        <v>0.2449869224062773</v>
       </c>
       <c r="T4" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="U4" t="n">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1784386617100372</v>
+        <v>0.1765475152571927</v>
       </c>
       <c r="W4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="X4" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.04739776951672862</v>
+        <v>0.04751525719267655</v>
       </c>
       <c r="Z4" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="AA4" t="n">
-        <v>699</v>
+        <v>745</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.324814126394052</v>
+        <v>0.3247602441150828</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7806167400881058</v>
+        <v>0.7786131996658312</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4631782945736434</v>
+        <v>0.4590747330960854</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.359375</v>
+        <v>0.3604938271604938</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.4128440366972477</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.3133047210300429</v>
+        <v>0.3140939597315436</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.561233480176212</v>
+        <v>1.557226399331662</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.71875</v>
+        <v>0.7209876543209877</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.9775280898876404</v>
+        <v>0.9800936768149883</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7819025522041764</v>
+        <v>0.7626373626373626</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.011799410029498</v>
+        <v>1.005434782608696</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.682242990654206</v>
+        <v>1.695652173913043</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.295399515738499</v>
+        <v>1.304545454545454</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.210653753026635</v>
+        <v>5.213636363636364</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.506053268765133</v>
+        <v>6.518181818181819</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.96749999999997</v>
+        <v>78.95764705882351</v>
       </c>
       <c r="C5" t="n">
-        <v>78.91562500000001</v>
+        <v>78.84764705882354</v>
       </c>
       <c r="D5" t="n">
-        <v>110.0067318734408</v>
+        <v>110.0409576174454</v>
       </c>
       <c r="E5" t="n">
-        <v>118.6789688353859</v>
+        <v>118.508516051059</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5220724907063197</v>
+        <v>0.5211421098517872</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1441052910717526</v>
+        <v>0.1441413108997039</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2872881355932204</v>
+        <v>0.2913697545526524</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2467472118959108</v>
+        <v>0.2436791630340018</v>
       </c>
       <c r="J5" t="n">
-        <v>10.53125</v>
+        <v>10.20588235294118</v>
       </c>
       <c r="K5" t="n">
-        <v>10.71875</v>
+        <v>10.88235294117647</v>
       </c>
       <c r="L5" t="n">
-        <v>5.625</v>
+        <v>5.735294117647059</v>
       </c>
       <c r="M5" t="n">
-        <v>11.96875</v>
+        <v>11.97058823529412</v>
       </c>
       <c r="N5" t="n">
-        <v>27.6875</v>
+        <v>27.41176470588235</v>
       </c>
       <c r="O5" t="n">
-        <v>35.46875</v>
+        <v>35.20588235294117</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5274163568773235</v>
+        <v>0.5217959895379249</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.46875</v>
+        <v>7.588235294117647</v>
       </c>
       <c r="R5" t="n">
-        <v>16.125</v>
+        <v>16.52941176470588</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2397769516728624</v>
+        <v>0.2449869224062773</v>
       </c>
       <c r="T5" t="n">
-        <v>4.3125</v>
+        <v>4.294117647058823</v>
       </c>
       <c r="U5" t="n">
-        <v>12</v>
+        <v>11.91176470588235</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1784386617100372</v>
+        <v>0.1765475152571927</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3125</v>
+        <v>1.323529411764706</v>
       </c>
       <c r="X5" t="n">
-        <v>3.1875</v>
+        <v>3.205882352941177</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.04739776951672862</v>
+        <v>0.04751525719267655</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.84375</v>
+        <v>6.882352941176471</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.84375</v>
+        <v>21.91176470588235</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.324814126394052</v>
+        <v>0.3247602441150828</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7806167400881058</v>
+        <v>0.7786131996658313</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4631782945736434</v>
+        <v>0.4590747330960853</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.359375</v>
+        <v>0.3604938271604938</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.4128440366972477</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3133047210300429</v>
+        <v>0.3140939597315436</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.561233480176212</v>
+        <v>1.557226399331663</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.71875</v>
+        <v>0.7209876543209877</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.9775280898876404</v>
+        <v>0.9800936768149884</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7819025522041764</v>
+        <v>0.7626373626373626</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.011799410029498</v>
+        <v>1.005434782608696</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.682242990654206</v>
+        <v>1.695652173913043</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.295399515738499</v>
+        <v>1.304545454545454</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.210653753026635</v>
+        <v>5.213636363636364</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.506053268765133</v>
+        <v>6.518181818181818</v>
       </c>
     </row>
     <row r="7">
@@ -1559,16 +1559,16 @@
         <v>0.607</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.283</v>
+        <v>0.285</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AX8" t="n">
         <v>0.031</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.018</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="9">
@@ -1578,43 +1578,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
-        <v>291</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E9" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G9" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H9" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="I9" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="J9" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K9" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N9" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1626,13 +1626,13 @@
         <v>33</v>
       </c>
       <c r="R9" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="S9" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="T9" t="n">
-        <v>389</v>
+        <v>426</v>
       </c>
       <c r="U9" t="n">
         <v>43</v>
@@ -1641,93 +1641,93 @@
         <v>29</v>
       </c>
       <c r="W9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="X9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="Z9" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.776</v>
+        <v>0.791</v>
       </c>
       <c r="AB9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AC9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.6</v>
+        <v>0.622</v>
       </c>
       <c r="AE9" t="n">
         <v>4</v>
       </c>
       <c r="AF9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AH9" t="n">
         <v>8</v>
       </c>
       <c r="AI9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.348</v>
+        <v>0.333</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.37</v>
+        <v>0.408</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>631:14</t>
+          <t>677:37</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>252.56</v>
+        <v>268.08</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.628</v>
+        <v>0.633</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.663</v>
+        <v>0.672</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.152</v>
+        <v>1.179</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.131</v>
+        <v>0.123</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.299</v>
+        <v>0.322</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.152</v>
+        <v>1.273</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="AW9" t="n">
         <v>0.08400000000000001</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.167</v>
+        <v>0.165</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.042</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="10">
@@ -1737,91 +1737,91 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E10" t="n">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F10" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G10" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H10" t="n">
+        <v>53</v>
+      </c>
+      <c r="I10" t="n">
+        <v>66</v>
+      </c>
+      <c r="J10" t="n">
+        <v>66</v>
+      </c>
+      <c r="K10" t="n">
         <v>46</v>
-      </c>
-      <c r="I10" t="n">
-        <v>59</v>
-      </c>
-      <c r="J10" t="n">
-        <v>60</v>
-      </c>
-      <c r="K10" t="n">
-        <v>44</v>
       </c>
       <c r="L10" t="n">
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R10" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="S10" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="T10" t="n">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="U10" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="V10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="W10" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Y10" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="Z10" t="n">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.775</v>
+        <v>0.79</v>
       </c>
       <c r="AB10" t="n">
         <v>29</v>
       </c>
       <c r="AC10" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.58</v>
+        <v>0.547</v>
       </c>
       <c r="AE10" t="n">
         <v>7</v>
@@ -1833,60 +1833,60 @@
         <v>0.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.412</v>
+        <v>0.444</v>
       </c>
       <c r="AK10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AL10" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AM10" t="n">
         <v>0.408</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>534:52</t>
+          <t>579:24</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>275.96</v>
+        <v>296.04</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.619</v>
+        <v>0.62</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.648</v>
+        <v>0.653</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.109</v>
+        <v>1.121</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.145</v>
+        <v>0.142</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.219</v>
+        <v>0.236</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.5</v>
+        <v>1.571</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.231</v>
+        <v>0.23</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.089</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.067</v>
+        <v>0.06900000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -2036,7 +2036,7 @@
         <v>1.467</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.246</v>
+        <v>0.247</v>
       </c>
       <c r="AW11" t="n">
         <v>0.053</v>
@@ -2045,7 +2045,7 @@
         <v>0.107</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.022</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="12">
@@ -2055,64 +2055,64 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F12" t="n">
         <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I12" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L12" t="n">
         <v>14</v>
       </c>
       <c r="M12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="N12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>18</v>
+      </c>
+      <c r="R12" t="n">
+        <v>49</v>
+      </c>
+      <c r="S12" t="n">
+        <v>44</v>
+      </c>
+      <c r="T12" t="n">
+        <v>161</v>
+      </c>
+      <c r="U12" t="n">
         <v>8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>17</v>
-      </c>
-      <c r="R12" t="n">
-        <v>48</v>
-      </c>
-      <c r="S12" t="n">
-        <v>40</v>
-      </c>
-      <c r="T12" t="n">
-        <v>150</v>
-      </c>
-      <c r="U12" t="n">
-        <v>6</v>
       </c>
       <c r="V12" t="n">
         <v>12</v>
@@ -2124,13 +2124,13 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.78</v>
+        <v>0.766</v>
       </c>
       <c r="AB12" t="n">
         <v>7</v>
@@ -2154,10 +2154,10 @@
         <v>2</v>
       </c>
       <c r="AI12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AK12" t="n">
         <v>3</v>
@@ -2170,41 +2170,41 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>402:14</t>
+          <t>424:45</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>83.56</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.58</v>
+        <v>0.578</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.616</v>
+        <v>0.615</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="AS12" t="n">
         <v>0.203</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.304</v>
+        <v>0.345</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.471</v>
+        <v>2.389</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="AW12" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AY12" t="n">
         <v>0.041</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0.043</v>
       </c>
     </row>
     <row r="13">
@@ -2214,100 +2214,100 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H13" t="n">
+        <v>44</v>
+      </c>
+      <c r="I13" t="n">
+        <v>57</v>
+      </c>
+      <c r="J13" t="n">
         <v>38</v>
       </c>
-      <c r="I13" t="n">
-        <v>51</v>
-      </c>
-      <c r="J13" t="n">
-        <v>34</v>
-      </c>
       <c r="K13" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="L13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="N13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="Q13" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="R13" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="S13" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="T13" t="n">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="U13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="V13" t="n">
         <v>25</v>
       </c>
       <c r="W13" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="X13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="Z13" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.804</v>
+        <v>0.824</v>
       </c>
       <c r="AB13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC13" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.444</v>
+        <v>0.433</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="AH13" t="n">
         <v>1</v>
@@ -2319,51 +2319,51 @@
         <v>0.143</v>
       </c>
       <c r="AK13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL13" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.375</v>
+        <v>0.378</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>363:47</t>
+          <t>401:49</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>184.44</v>
+        <v>207.08</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.612</v>
+        <v>0.616</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.649</v>
+        <v>0.657</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.003</v>
+        <v>1.009</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.228</v>
+        <v>0.232</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.317</v>
+        <v>0.328</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.792</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.227</v>
+        <v>0.232</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.11</v>
+        <v>0.113</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.036</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="14">
@@ -2513,16 +2513,16 @@
         <v>1.133</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.292</v>
+        <v>0.294</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.066</v>
+        <v>0.067</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.232</v>
+        <v>0.23</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="15">
@@ -2532,40 +2532,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C15" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="D15" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E15" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G15" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I15" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="J15" t="n">
         <v>40</v>
       </c>
       <c r="K15" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="L15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="M15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N15" t="n">
         <v>13</v>
@@ -2574,19 +2574,19 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Q15" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="R15" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="S15" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="T15" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="U15" t="n">
         <v>22</v>
@@ -2601,87 +2601,87 @@
         <v>15</v>
       </c>
       <c r="Y15" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Z15" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.649</v>
+        <v>0.643</v>
       </c>
       <c r="AB15" t="n">
         <v>19</v>
       </c>
       <c r="AC15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.475</v>
+        <v>0.452</v>
       </c>
       <c r="AE15" t="n">
         <v>3</v>
       </c>
       <c r="AF15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG15" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>73</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>514:20</t>
+        </is>
+      </c>
+      <c r="AO15" t="n">
+        <v>228.88</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="AV15" t="n">
         <v>0.2</v>
       </c>
-      <c r="AH15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>67</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>476:07</t>
-        </is>
-      </c>
-      <c r="AO15" t="n">
-        <v>209.68</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.176</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0.197</v>
-      </c>
       <c r="AW15" t="n">
-        <v>0.074</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.155</v>
+        <v>0.157</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="16">
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>59</v>
@@ -2700,13 +2700,13 @@
         <v>15</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
         <v>7</v>
       </c>
       <c r="G16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H16" t="n">
         <v>8</v>
@@ -2715,10 +2715,10 @@
         <v>11</v>
       </c>
       <c r="J16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K16" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="L16" t="n">
         <v>11</v>
@@ -2727,7 +2727,7 @@
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2742,10 +2742,10 @@
         <v>15</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="U16" t="n">
         <v>2</v>
@@ -2763,19 +2763,19 @@
         <v>15</v>
       </c>
       <c r="Z16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="AB16" t="n">
         <v>4</v>
       </c>
       <c r="AC16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -2790,57 +2790,57 @@
         <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AK16" t="n">
         <v>5</v>
       </c>
       <c r="AL16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.357</v>
+        <v>0.333</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>164:14</t>
+          <t>184:49</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>52.84</v>
+        <v>56.84</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.593</v>
+        <v>0.543</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.617</v>
+        <v>0.569</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.117</v>
+        <v>1.038</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.095</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.186</v>
+        <v>0.17</v>
       </c>
       <c r="AU16" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.144</v>
+        <v>0.139</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.079</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.185</v>
+        <v>0.175</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="17">
@@ -2850,156 +2850,156 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C17" t="n">
-        <v>555</v>
+        <v>598</v>
       </c>
       <c r="D17" t="n">
+        <v>97</v>
+      </c>
+      <c r="E17" t="n">
+        <v>177</v>
+      </c>
+      <c r="F17" t="n">
         <v>86</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
+        <v>219</v>
+      </c>
+      <c r="H17" t="n">
+        <v>146</v>
+      </c>
+      <c r="I17" t="n">
         <v>162</v>
       </c>
-      <c r="F17" t="n">
-        <v>81</v>
-      </c>
-      <c r="G17" t="n">
-        <v>206</v>
-      </c>
-      <c r="H17" t="n">
-        <v>140</v>
-      </c>
-      <c r="I17" t="n">
-        <v>156</v>
-      </c>
       <c r="J17" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K17" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="L17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N17" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="Q17" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="R17" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="S17" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="T17" t="n">
-        <v>546</v>
+        <v>586</v>
       </c>
       <c r="U17" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="V17" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="W17" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="X17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y17" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="Z17" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.861</v>
+        <v>0.867</v>
       </c>
       <c r="AB17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>53</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="AE17" t="n">
         <v>23</v>
       </c>
-      <c r="AC17" t="n">
-        <v>51</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>17</v>
-      </c>
       <c r="AF17" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.333</v>
+        <v>0.383</v>
       </c>
       <c r="AH17" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AI17" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.549</v>
+        <v>0.526</v>
       </c>
       <c r="AK17" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AL17" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.342</v>
+        <v>0.346</v>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>693:46</t>
+          <t>740:17</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>481.64</v>
+        <v>515.28</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.636</v>
+        <v>0.64</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.152</v>
+        <v>1.161</v>
       </c>
       <c r="AS17" t="n">
         <v>0.093</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.38</v>
+        <v>0.369</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.311</v>
+        <v>0.314</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.037</v>
+        <v>0.04</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.139</v>
+        <v>0.137</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
     </row>
     <row r="18">
@@ -3009,40 +3009,40 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C18" t="n">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="D18" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E18" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H18" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="I18" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J18" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K18" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L18" t="n">
         <v>13</v>
       </c>
       <c r="M18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N18" t="n">
         <v>20</v>
@@ -3051,22 +3051,22 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="Q18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R18" t="n">
+        <v>54</v>
+      </c>
+      <c r="S18" t="n">
+        <v>74</v>
+      </c>
+      <c r="T18" t="n">
+        <v>321</v>
+      </c>
+      <c r="U18" t="n">
         <v>51</v>
-      </c>
-      <c r="S18" t="n">
-        <v>69</v>
-      </c>
-      <c r="T18" t="n">
-        <v>303</v>
-      </c>
-      <c r="U18" t="n">
-        <v>46</v>
       </c>
       <c r="V18" t="n">
         <v>24</v>
@@ -3078,31 +3078,31 @@
         <v>17</v>
       </c>
       <c r="Y18" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="Z18" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.804</v>
+        <v>0.788</v>
       </c>
       <c r="AB18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC18" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.436</v>
+        <v>0.446</v>
       </c>
       <c r="AE18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.381</v>
+        <v>0.395</v>
       </c>
       <c r="AH18" t="n">
         <v>3</v>
@@ -3114,51 +3114,51 @@
         <v>0.231</v>
       </c>
       <c r="AK18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>604:14</t>
+          <t>639:00</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>237.52</v>
+        <v>247.16</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.511</v>
+        <v>0.522</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.977</v>
+        <v>0.987</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.139</v>
+        <v>0.142</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.274</v>
+        <v>0.283</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.939</v>
+        <v>1.914</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.176</v>
+        <v>0.174</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.118</v>
+        <v>0.121</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="19">
@@ -3168,64 +3168,64 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>23</v>
+      </c>
+      <c r="C19" t="n">
+        <v>324</v>
+      </c>
+      <c r="D19" t="n">
+        <v>70</v>
+      </c>
+      <c r="E19" t="n">
+        <v>116</v>
+      </c>
+      <c r="F19" t="n">
         <v>21</v>
       </c>
-      <c r="C19" t="n">
-        <v>303</v>
-      </c>
-      <c r="D19" t="n">
-        <v>67</v>
-      </c>
-      <c r="E19" t="n">
-        <v>109</v>
-      </c>
-      <c r="F19" t="n">
-        <v>18</v>
-      </c>
       <c r="G19" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H19" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="I19" t="n">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="J19" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K19" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="L19" t="n">
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="R19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S19" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="T19" t="n">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="U19" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="V19" t="n">
         <v>33</v>
@@ -3237,87 +3237,87 @@
         <v>12</v>
       </c>
       <c r="Y19" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="Z19" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.896</v>
+        <v>0.895</v>
       </c>
       <c r="AB19" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AC19" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.528</v>
+        <v>0.526</v>
       </c>
       <c r="AE19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.421</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI19" t="n">
         <v>17</v>
       </c>
-      <c r="AG19" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>16</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>0.188</v>
+        <v>0.235</v>
       </c>
       <c r="AK19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL19" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.319</v>
+        <v>0.315</v>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>534:18</t>
+          <t>589:01</t>
         </is>
       </c>
       <c r="AO19" t="n">
-        <v>269</v>
+        <v>288.64</v>
       </c>
       <c r="AP19" t="n">
-        <v>0.547</v>
+        <v>0.543</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.667</v>
+        <v>0.662</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.126</v>
+        <v>1.123</v>
       </c>
       <c r="AS19" t="n">
-        <v>0.156</v>
+        <v>0.152</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.669</v>
+        <v>0.647</v>
       </c>
       <c r="AU19" t="n">
-        <v>2</v>
+        <v>2.045</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.226</v>
+        <v>0.221</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.13</v>
+        <v>0.132</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.091</v>
+        <v>0.092</v>
       </c>
     </row>
     <row r="20">
@@ -3327,16 +3327,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E20" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3351,10 +3351,10 @@
         <v>34</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L20" t="n">
         <v>19</v>
@@ -3369,19 +3369,19 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R20" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
       </c>
       <c r="T20" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="U20" t="n">
         <v>6</v>
@@ -3396,22 +3396,22 @@
         <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Z20" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.618</v>
+        <v>0.625</v>
       </c>
       <c r="AB20" t="n">
         <v>2</v>
       </c>
       <c r="AC20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.2</v>
+        <v>0.182</v>
       </c>
       <c r="AE20" t="n">
         <v>2</v>
@@ -3442,41 +3442,41 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>148:48</t>
+          <t>160:11</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>61.96</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.541</v>
+        <v>0.538</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.924</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.161</v>
+        <v>0.169</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.486</v>
+        <v>0.462</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.3</v>
+        <v>0.364</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.187</v>
+        <v>0.183</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AX20" t="n">
         <v>0.175</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="21">
@@ -3486,40 +3486,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J21" t="n">
+        <v>30</v>
+      </c>
+      <c r="K21" t="n">
+        <v>53</v>
+      </c>
+      <c r="L21" t="n">
         <v>28</v>
       </c>
-      <c r="K21" t="n">
-        <v>51</v>
-      </c>
-      <c r="L21" t="n">
-        <v>26</v>
-      </c>
       <c r="M21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N21" t="n">
         <v>4</v>
@@ -3528,25 +3528,25 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R21" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="S21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T21" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="U21" t="n">
         <v>11</v>
       </c>
       <c r="V21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W21" t="n">
         <v>7</v>
@@ -3555,84 +3555,84 @@
         <v>4</v>
       </c>
       <c r="Y21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.64</v>
+        <v>0.667</v>
       </c>
       <c r="AB21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.714</v>
       </c>
       <c r="AE21" t="n">
         <v>6</v>
       </c>
       <c r="AF21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AI21" t="n">
         <v>18</v>
       </c>
-      <c r="AG21" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>16</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>0.375</v>
+        <v>0.389</v>
       </c>
       <c r="AK21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.5</v>
+        <v>0.519</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>432:03</t>
+          <t>469:22</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>106.28</v>
+        <v>113.16</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.61</v>
+        <v>0.621</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.613</v>
+        <v>0.628</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.054</v>
+        <v>1.078</v>
       </c>
       <c r="AS21" t="n">
         <v>0.141</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.081</v>
+        <v>0.099</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.867</v>
+        <v>1.875</v>
       </c>
       <c r="AV21" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="AW21" t="n">
         <v>0.07099999999999999</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.128</v>
+        <v>0.122</v>
       </c>
       <c r="AY21" t="n">
         <v>0.029</v>
@@ -3785,16 +3785,16 @@
         <v>0.85</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="AW22" t="n">
-        <v>0.089</v>
+        <v>0.09</v>
       </c>
       <c r="AX22" t="n">
-        <v>0.211</v>
+        <v>0.209</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.017</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="23">
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>0.325</v>
+        <v>0.327</v>
       </c>
       <c r="AW23" t="n">
         <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>0.203</v>
+        <v>0.201</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" t="n">
         <v>134</v>
@@ -3972,13 +3972,13 @@
         <v>20</v>
       </c>
       <c r="E24" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F24" t="n">
         <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H24" t="n">
         <v>10</v>
@@ -3990,7 +3990,7 @@
         <v>12</v>
       </c>
       <c r="K24" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L24" t="n">
         <v>27</v>
@@ -4053,10 +4053,10 @@
         <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG24" t="n">
-        <v>0.118</v>
+        <v>0.111</v>
       </c>
       <c r="AH24" t="n">
         <v>12</v>
@@ -4071,45 +4071,45 @@
         <v>16</v>
       </c>
       <c r="AL24" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.32</v>
+        <v>0.314</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>415:36</t>
+          <t>420:38</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>135.28</v>
+        <v>137.28</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.5</v>
+        <v>0.492</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.518</v>
+        <v>0.51</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.991</v>
+        <v>0.976</v>
       </c>
       <c r="AS24" t="n">
         <v>0.044</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="AU24" t="n">
         <v>2</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.146</v>
+        <v>0.147</v>
       </c>
       <c r="AW24" t="n">
         <v>0.076</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.167</v>
+        <v>0.169</v>
       </c>
       <c r="AY24" t="n">
         <v>0.012</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.212</v>
+        <v>0.213</v>
       </c>
       <c r="AW25" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="AX25" t="n">
         <v>0</v>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.129</v>
+        <v>0.13</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.12</v>
+        <v>0.119</v>
       </c>
       <c r="AY26" t="n">
         <v>0</v>
@@ -4580,16 +4580,16 @@
         <v>1.125</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.198</v>
+        <v>0.199</v>
       </c>
       <c r="AW27" t="n">
         <v>0.057</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.008</v>
       </c>
     </row>
     <row r="28">
@@ -4739,13 +4739,13 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>0.267</v>
+        <v>0.268</v>
       </c>
       <c r="AW28" t="n">
         <v>0.051</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.141</v>
+        <v>0.14</v>
       </c>
       <c r="AY28" t="n">
         <v>0.002</v>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -4785,7 +4785,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L29" t="n">
         <v>40</v>
@@ -4800,7 +4800,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -4917,153 +4917,153 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C30" t="n">
-        <v>2997</v>
+        <v>3177</v>
       </c>
       <c r="D30" t="n">
-        <v>684</v>
+        <v>721</v>
       </c>
       <c r="E30" t="n">
-        <v>1185</v>
+        <v>1249</v>
       </c>
       <c r="F30" t="n">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="G30" t="n">
-        <v>885</v>
+        <v>938</v>
       </c>
       <c r="H30" t="n">
-        <v>645</v>
+        <v>688</v>
       </c>
       <c r="I30" t="n">
-        <v>806</v>
+        <v>857</v>
       </c>
       <c r="J30" t="n">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="K30" t="n">
-        <v>841</v>
+        <v>895</v>
       </c>
       <c r="L30" t="n">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="M30" t="n">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="N30" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="Q30" t="n">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="R30" t="n">
-        <v>703</v>
+        <v>747</v>
       </c>
       <c r="S30" t="n">
-        <v>725</v>
+        <v>770</v>
       </c>
       <c r="T30" t="n">
-        <v>3553</v>
+        <v>3764</v>
       </c>
       <c r="U30" t="n">
-        <v>399</v>
+        <v>424</v>
       </c>
       <c r="V30" t="n">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="W30" t="n">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="X30" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="Y30" t="n">
-        <v>1027</v>
+        <v>1091</v>
       </c>
       <c r="Z30" t="n">
-        <v>1293</v>
+        <v>1368</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.794</v>
+        <v>0.798</v>
       </c>
       <c r="AB30" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="AC30" t="n">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="AD30" t="n">
-        <v>0.503</v>
+        <v>0.499</v>
       </c>
       <c r="AE30" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="AF30" t="n">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="AG30" t="n">
-        <v>0.318</v>
+        <v>0.324</v>
       </c>
       <c r="AH30" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="AI30" t="n">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="AJ30" t="n">
         <v>0.388</v>
       </c>
       <c r="AK30" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AL30" t="n">
-        <v>676</v>
+        <v>714</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>6400:00</t>
+          <t>6800:00</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>2855.64</v>
+        <v>3019.08</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.618</v>
+        <v>0.62</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.05</v>
+        <v>1.052</v>
       </c>
       <c r="AS30" t="n">
         <v>0.151</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.312</v>
+        <v>0.315</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.283</v>
+        <v>1.284</v>
       </c>
       <c r="AV30" t="n">
         <v>0.2</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
       <c r="AY30" t="n">
         <v>0</v>
@@ -5076,153 +5076,153 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>2778</v>
+        <v>2950</v>
       </c>
       <c r="D31" t="n">
-        <v>732</v>
+        <v>777</v>
       </c>
       <c r="E31" t="n">
-        <v>1351</v>
+        <v>1440</v>
       </c>
       <c r="F31" t="n">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="G31" t="n">
-        <v>801</v>
+        <v>854</v>
       </c>
       <c r="H31" t="n">
-        <v>531</v>
+        <v>559</v>
       </c>
       <c r="I31" t="n">
-        <v>684</v>
+        <v>724</v>
       </c>
       <c r="J31" t="n">
-        <v>535</v>
+        <v>574</v>
       </c>
       <c r="K31" t="n">
-        <v>760</v>
+        <v>808</v>
       </c>
       <c r="L31" t="n">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="M31" t="n">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="N31" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="Q31" t="n">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="R31" t="n">
-        <v>736</v>
+        <v>782</v>
       </c>
       <c r="S31" t="n">
-        <v>702</v>
+        <v>747</v>
       </c>
       <c r="T31" t="n">
-        <v>3073</v>
+        <v>3265</v>
       </c>
       <c r="U31" t="n">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="V31" t="n">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="W31" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="X31" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="Y31" t="n">
-        <v>886</v>
+        <v>932</v>
       </c>
       <c r="Z31" t="n">
-        <v>1135</v>
+        <v>1197</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="AB31" t="n">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="AC31" t="n">
-        <v>516</v>
+        <v>562</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.463</v>
+        <v>0.459</v>
       </c>
       <c r="AE31" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="AF31" t="n">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="AG31" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="AI31" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.412</v>
+        <v>0.413</v>
       </c>
       <c r="AK31" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="AL31" t="n">
-        <v>699</v>
+        <v>745</v>
       </c>
       <c r="AM31" t="n">
-        <v>0.313</v>
+        <v>0.314</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>6400:00</t>
+          <t>6800:00</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>2865.96</v>
+        <v>3052.56</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.522</v>
+        <v>0.521</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.969</v>
+        <v>0.966</v>
       </c>
       <c r="AS31" t="n">
         <v>0.144</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.247</v>
+        <v>0.244</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.295</v>
+        <v>1.305</v>
       </c>
       <c r="AV31" t="n">
         <v>0.2</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.057</v>
+        <v>0.058</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.139</v>
+        <v>0.141</v>
       </c>
       <c r="AY31" t="n">
         <v>0</v>
@@ -5432,10 +5432,10 @@
         <v>0.607</v>
       </c>
       <c r="AV33" t="n">
-        <v>0.283</v>
+        <v>0.285</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.008</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AX33" t="n">
         <v>0.031</v>
@@ -5451,156 +5451,156 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>9.387</v>
+        <v>9.576000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>2.581</v>
+        <v>2.545</v>
       </c>
       <c r="E34" t="n">
-        <v>3.806</v>
+        <v>3.818</v>
       </c>
       <c r="F34" t="n">
-        <v>0.806</v>
+        <v>0.848</v>
       </c>
       <c r="G34" t="n">
-        <v>2.226</v>
+        <v>2.212</v>
       </c>
       <c r="H34" t="n">
-        <v>1.806</v>
+        <v>1.939</v>
       </c>
       <c r="I34" t="n">
-        <v>2.387</v>
+        <v>2.485</v>
       </c>
       <c r="J34" t="n">
-        <v>1.226</v>
+        <v>1.273</v>
       </c>
       <c r="K34" t="n">
-        <v>3.129</v>
+        <v>3.152</v>
       </c>
       <c r="L34" t="n">
-        <v>1.452</v>
+        <v>1.455</v>
       </c>
       <c r="M34" t="n">
-        <v>0.323</v>
+        <v>0.364</v>
       </c>
       <c r="N34" t="n">
-        <v>1.968</v>
+        <v>1.909</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.065</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.065</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>2.613</v>
+        <v>2.667</v>
       </c>
       <c r="S34" t="n">
-        <v>1.968</v>
+        <v>2.03</v>
       </c>
       <c r="T34" t="n">
-        <v>389</v>
+        <v>426</v>
       </c>
       <c r="U34" t="n">
-        <v>1.387</v>
+        <v>1.303</v>
       </c>
       <c r="V34" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.879</v>
       </c>
       <c r="W34" t="n">
-        <v>0.645</v>
+        <v>0.758</v>
       </c>
       <c r="X34" t="n">
-        <v>0.355</v>
+        <v>0.424</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.581</v>
+        <v>3.667</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.613</v>
+        <v>4.636</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.776</v>
+        <v>0.791</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.677</v>
+        <v>0.697</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.129</v>
+        <v>1.121</v>
       </c>
       <c r="AD34" t="n">
-        <v>0.6</v>
+        <v>0.622</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.129</v>
+        <v>0.121</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.452</v>
+        <v>0.545</v>
       </c>
       <c r="AG34" t="n">
-        <v>0.286</v>
+        <v>0.222</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.258</v>
+        <v>0.242</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.742</v>
+        <v>0.727</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.348</v>
+        <v>0.333</v>
       </c>
       <c r="AK34" t="n">
-        <v>0.548</v>
+        <v>0.606</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.484</v>
+        <v>1.485</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.37</v>
+        <v>0.408</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>8.147</v>
+        <v>8.124000000000001</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.628</v>
+        <v>0.633</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.663</v>
+        <v>0.672</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.152</v>
+        <v>1.179</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.131</v>
+        <v>0.123</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.299</v>
+        <v>0.322</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.152</v>
+        <v>1.273</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
       <c r="AW34" t="n">
         <v>0.08400000000000001</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.167</v>
+        <v>0.165</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.043</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="35">
@@ -5610,115 +5610,115 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C35" t="n">
-        <v>12.75</v>
+        <v>12.769</v>
       </c>
       <c r="D35" t="n">
-        <v>3.167</v>
+        <v>3.115</v>
       </c>
       <c r="E35" t="n">
-        <v>5.083</v>
+        <v>5.038</v>
       </c>
       <c r="F35" t="n">
         <v>1.5</v>
       </c>
       <c r="G35" t="n">
-        <v>3.667</v>
+        <v>3.615</v>
       </c>
       <c r="H35" t="n">
-        <v>1.917</v>
+        <v>2.038</v>
       </c>
       <c r="I35" t="n">
-        <v>2.458</v>
+        <v>2.538</v>
       </c>
       <c r="J35" t="n">
-        <v>2.5</v>
+        <v>2.538</v>
       </c>
       <c r="K35" t="n">
-        <v>1.833</v>
+        <v>1.769</v>
       </c>
       <c r="L35" t="n">
-        <v>0.417</v>
+        <v>0.385</v>
       </c>
       <c r="M35" t="n">
-        <v>0.625</v>
+        <v>0.615</v>
       </c>
       <c r="N35" t="n">
-        <v>0.292</v>
+        <v>0.308</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>1.667</v>
+        <v>1.615</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.667</v>
+        <v>1.615</v>
       </c>
       <c r="R35" t="n">
-        <v>3.167</v>
+        <v>3.077</v>
       </c>
       <c r="S35" t="n">
-        <v>2.375</v>
+        <v>2.346</v>
       </c>
       <c r="T35" t="n">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="U35" t="n">
-        <v>1.417</v>
+        <v>1.423</v>
       </c>
       <c r="V35" t="n">
-        <v>1.042</v>
+        <v>1.077</v>
       </c>
       <c r="W35" t="n">
-        <v>1.083</v>
+        <v>1.077</v>
       </c>
       <c r="X35" t="n">
-        <v>0.708</v>
+        <v>0.731</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.583</v>
+        <v>3.769</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.625</v>
+        <v>4.769</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.775</v>
+        <v>0.79</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.208</v>
+        <v>1.115</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.083</v>
+        <v>2.038</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.58</v>
+        <v>0.547</v>
       </c>
       <c r="AE35" t="n">
-        <v>0.292</v>
+        <v>0.269</v>
       </c>
       <c r="AF35" t="n">
-        <v>0.833</v>
+        <v>0.769</v>
       </c>
       <c r="AG35" t="n">
         <v>0.35</v>
       </c>
       <c r="AH35" t="n">
-        <v>0.292</v>
+        <v>0.308</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.708</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.412</v>
+        <v>0.444</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.208</v>
+        <v>1.192</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.958</v>
+        <v>2.923</v>
       </c>
       <c r="AM35" t="n">
         <v>0.408</v>
@@ -5729,37 +5729,37 @@
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>11.498</v>
+        <v>11.386</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.619</v>
+        <v>0.62</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.648</v>
+        <v>0.653</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.109</v>
+        <v>1.121</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.145</v>
+        <v>0.142</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.219</v>
+        <v>0.236</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.5</v>
+        <v>1.571</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.231</v>
+        <v>0.23</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.089</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.093</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="36">
@@ -5909,7 +5909,7 @@
         <v>1.467</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.246</v>
+        <v>0.247</v>
       </c>
       <c r="AW36" t="n">
         <v>0.053</v>
@@ -5918,7 +5918,7 @@
         <v>0.107</v>
       </c>
       <c r="AY36" t="n">
-        <v>0.126</v>
+        <v>0.127</v>
       </c>
     </row>
     <row r="37">
@@ -5928,156 +5928,156 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C37" t="n">
-        <v>2.562</v>
+        <v>2.559</v>
       </c>
       <c r="D37" t="n">
-        <v>0.781</v>
+        <v>0.765</v>
       </c>
       <c r="E37" t="n">
-        <v>1.25</v>
+        <v>1.206</v>
       </c>
       <c r="F37" t="n">
-        <v>0.156</v>
+        <v>0.147</v>
       </c>
       <c r="G37" t="n">
         <v>0.5</v>
       </c>
       <c r="H37" t="n">
-        <v>0.531</v>
+        <v>0.588</v>
       </c>
       <c r="I37" t="n">
-        <v>0.75</v>
+        <v>0.853</v>
       </c>
       <c r="J37" t="n">
-        <v>1.312</v>
+        <v>1.265</v>
       </c>
       <c r="K37" t="n">
-        <v>1.094</v>
+        <v>1.059</v>
       </c>
       <c r="L37" t="n">
-        <v>0.438</v>
+        <v>0.412</v>
       </c>
       <c r="M37" t="n">
-        <v>0.844</v>
+        <v>0.912</v>
       </c>
       <c r="N37" t="n">
-        <v>0.25</v>
+        <v>0.265</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.531</v>
+        <v>0.529</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.531</v>
+        <v>0.529</v>
       </c>
       <c r="R37" t="n">
-        <v>1.5</v>
+        <v>1.441</v>
       </c>
       <c r="S37" t="n">
-        <v>1.25</v>
+        <v>1.294</v>
       </c>
       <c r="T37" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="U37" t="n">
-        <v>0.188</v>
+        <v>0.235</v>
       </c>
       <c r="V37" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="W37" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="X37" t="n">
-        <v>0.25</v>
+        <v>0.235</v>
       </c>
       <c r="Y37" t="n">
-        <v>1</v>
+        <v>1.059</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.281</v>
+        <v>1.382</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.78</v>
+        <v>0.766</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="AD37" t="n">
         <v>0.438</v>
       </c>
       <c r="AE37" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AF37" t="n">
-        <v>0.219</v>
+        <v>0.206</v>
       </c>
       <c r="AG37" t="n">
         <v>0.429</v>
       </c>
       <c r="AH37" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.188</v>
+        <v>0.206</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.333</v>
+        <v>0.286</v>
       </c>
       <c r="AK37" t="n">
-        <v>0.094</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AL37" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="AM37" t="n">
         <v>0.3</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AO37" t="n">
         <v>2.611</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.58</v>
+        <v>0.578</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.616</v>
+        <v>0.615</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.981</v>
+        <v>0.98</v>
       </c>
       <c r="AS37" t="n">
         <v>0.203</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.304</v>
+        <v>0.345</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.471</v>
+        <v>2.389</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="AW37" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AY37" t="n">
         <v>0.041</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>0.043</v>
       </c>
     </row>
     <row r="38">
@@ -6087,156 +6087,156 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C38" t="n">
-        <v>8.042999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>2.348</v>
+        <v>2.4</v>
       </c>
       <c r="E38" t="n">
-        <v>3.522</v>
+        <v>3.6</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="G38" t="n">
-        <v>1.696</v>
+        <v>1.76</v>
       </c>
       <c r="H38" t="n">
-        <v>1.652</v>
+        <v>1.76</v>
       </c>
       <c r="I38" t="n">
-        <v>2.217</v>
+        <v>2.28</v>
       </c>
       <c r="J38" t="n">
-        <v>1.478</v>
+        <v>1.52</v>
       </c>
       <c r="K38" t="n">
-        <v>1.609</v>
+        <v>1.68</v>
       </c>
       <c r="L38" t="n">
-        <v>0.783</v>
+        <v>0.76</v>
       </c>
       <c r="M38" t="n">
-        <v>0.826</v>
+        <v>0.88</v>
       </c>
       <c r="N38" t="n">
-        <v>0.391</v>
+        <v>0.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.826</v>
+        <v>1.92</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.826</v>
+        <v>1.92</v>
       </c>
       <c r="R38" t="n">
-        <v>2.087</v>
+        <v>2.08</v>
       </c>
       <c r="S38" t="n">
-        <v>2.087</v>
+        <v>2.2</v>
       </c>
       <c r="T38" t="n">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="U38" t="n">
-        <v>1.304</v>
+        <v>1.28</v>
       </c>
       <c r="V38" t="n">
-        <v>1.087</v>
+        <v>1</v>
       </c>
       <c r="W38" t="n">
-        <v>0.609</v>
+        <v>0.76</v>
       </c>
       <c r="X38" t="n">
-        <v>0.304</v>
+        <v>0.4</v>
       </c>
       <c r="Y38" t="n">
-        <v>3.391</v>
+        <v>3.56</v>
       </c>
       <c r="Z38" t="n">
-        <v>4.217</v>
+        <v>4.32</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.804</v>
+        <v>0.824</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.522</v>
+        <v>0.52</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.174</v>
+        <v>1.2</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.444</v>
+        <v>0.433</v>
       </c>
       <c r="AE38" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08</v>
       </c>
       <c r="AF38" t="n">
-        <v>0.348</v>
+        <v>0.36</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.25</v>
+        <v>0.222</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.043</v>
+        <v>0.04</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.304</v>
+        <v>0.28</v>
       </c>
       <c r="AJ38" t="n">
         <v>0.143</v>
       </c>
       <c r="AK38" t="n">
-        <v>0.522</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.391</v>
+        <v>1.48</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.375</v>
+        <v>0.378</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>8.019</v>
+        <v>8.282999999999999</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.612</v>
+        <v>0.616</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.649</v>
+        <v>0.657</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.003</v>
+        <v>1.009</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.228</v>
+        <v>0.232</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.317</v>
+        <v>0.328</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.792</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.227</v>
+        <v>0.232</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.058</v>
+        <v>0.056</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.11</v>
+        <v>0.113</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.051</v>
+        <v>0.053</v>
       </c>
     </row>
     <row r="39">
@@ -6386,13 +6386,13 @@
         <v>1.133</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.292</v>
+        <v>0.294</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.066</v>
+        <v>0.067</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.232</v>
+        <v>0.23</v>
       </c>
       <c r="AY39" t="n">
         <v>0.079</v>
@@ -6405,156 +6405,156 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C40" t="n">
-        <v>8.5</v>
+        <v>8.308</v>
       </c>
       <c r="D40" t="n">
-        <v>1.75</v>
+        <v>1.692</v>
       </c>
       <c r="E40" t="n">
-        <v>3.542</v>
+        <v>3.462</v>
       </c>
       <c r="F40" t="n">
-        <v>1.25</v>
+        <v>1.231</v>
       </c>
       <c r="G40" t="n">
-        <v>2.917</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>1.25</v>
+        <v>1.231</v>
       </c>
       <c r="I40" t="n">
-        <v>1.958</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
-        <v>1.667</v>
+        <v>1.538</v>
       </c>
       <c r="K40" t="n">
-        <v>2.833</v>
+        <v>2.885</v>
       </c>
       <c r="L40" t="n">
-        <v>1.25</v>
+        <v>1.192</v>
       </c>
       <c r="M40" t="n">
-        <v>0.917</v>
+        <v>0.885</v>
       </c>
       <c r="N40" t="n">
-        <v>0.542</v>
+        <v>0.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>1.417</v>
+        <v>1.462</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.417</v>
+        <v>1.462</v>
       </c>
       <c r="R40" t="n">
-        <v>2.792</v>
+        <v>2.846</v>
       </c>
       <c r="S40" t="n">
-        <v>2.125</v>
+        <v>2.192</v>
       </c>
       <c r="T40" t="n">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="U40" t="n">
-        <v>0.917</v>
+        <v>0.846</v>
       </c>
       <c r="V40" t="n">
-        <v>0.958</v>
+        <v>0.885</v>
       </c>
       <c r="W40" t="n">
-        <v>0.958</v>
+        <v>0.885</v>
       </c>
       <c r="X40" t="n">
-        <v>0.625</v>
+        <v>0.577</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.083</v>
+        <v>2.077</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.208</v>
+        <v>3.231</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.649</v>
+        <v>0.643</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.792</v>
+        <v>0.731</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.667</v>
+        <v>1.615</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.475</v>
+        <v>0.452</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.125</v>
+        <v>0.115</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.625</v>
+        <v>0.615</v>
       </c>
       <c r="AG40" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>2.808</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="AO40" t="n">
+        <v>8.803000000000001</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0.166</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="AV40" t="n">
         <v>0.2</v>
       </c>
-      <c r="AH40" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.792</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>19:50</t>
-        </is>
-      </c>
-      <c r="AO40" t="n">
-        <v>8.737</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0.581</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0.194</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>1.176</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0.197</v>
-      </c>
       <c r="AW40" t="n">
-        <v>0.074</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.155</v>
+        <v>0.157</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.058</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="41">
@@ -6564,153 +6564,153 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C41" t="n">
-        <v>5.364</v>
+        <v>4.538</v>
       </c>
       <c r="D41" t="n">
-        <v>1.364</v>
+        <v>1.154</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>1.846</v>
       </c>
       <c r="F41" t="n">
-        <v>0.636</v>
+        <v>0.538</v>
       </c>
       <c r="G41" t="n">
-        <v>1.909</v>
+        <v>1.769</v>
       </c>
       <c r="H41" t="n">
-        <v>0.727</v>
+        <v>0.615</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0.846</v>
       </c>
       <c r="J41" t="n">
-        <v>0.909</v>
+        <v>0.923</v>
       </c>
       <c r="K41" t="n">
-        <v>2.545</v>
+        <v>2.308</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0.846</v>
       </c>
       <c r="M41" t="n">
-        <v>0.182</v>
+        <v>0.154</v>
       </c>
       <c r="N41" t="n">
-        <v>0.091</v>
+        <v>0.231</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.455</v>
+        <v>0.385</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.455</v>
+        <v>0.385</v>
       </c>
       <c r="R41" t="n">
-        <v>1.364</v>
+        <v>1.154</v>
       </c>
       <c r="S41" t="n">
-        <v>0.909</v>
+        <v>0.923</v>
       </c>
       <c r="T41" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="U41" t="n">
-        <v>0.182</v>
+        <v>0.154</v>
       </c>
       <c r="V41" t="n">
-        <v>0.727</v>
+        <v>0.615</v>
       </c>
       <c r="W41" t="n">
-        <v>0.364</v>
+        <v>0.308</v>
       </c>
       <c r="X41" t="n">
-        <v>0.273</v>
+        <v>0.231</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.364</v>
+        <v>1.154</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.818</v>
+        <v>1.615</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.364</v>
+        <v>0.308</v>
       </c>
       <c r="AC41" t="n">
-        <v>0.727</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AD41" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="AE41" t="n">
-        <v>0.364</v>
+        <v>0.308</v>
       </c>
       <c r="AF41" t="n">
-        <v>0.455</v>
+        <v>0.385</v>
       </c>
       <c r="AG41" t="n">
         <v>0.8</v>
       </c>
       <c r="AH41" t="n">
-        <v>0.182</v>
+        <v>0.154</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.636</v>
+        <v>0.615</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.286</v>
+        <v>0.25</v>
       </c>
       <c r="AK41" t="n">
-        <v>0.455</v>
+        <v>0.385</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.273</v>
+        <v>1.154</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.357</v>
+        <v>0.333</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>4.804</v>
+        <v>4.372</v>
       </c>
       <c r="AP41" t="n">
-        <v>0.593</v>
+        <v>0.543</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.617</v>
+        <v>0.569</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.117</v>
+        <v>1.038</v>
       </c>
       <c r="AS41" t="n">
-        <v>0.095</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT41" t="n">
-        <v>0.186</v>
+        <v>0.17</v>
       </c>
       <c r="AU41" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.144</v>
+        <v>0.139</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.079</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.185</v>
+        <v>0.175</v>
       </c>
       <c r="AY41" t="n">
         <v>0.031</v>
@@ -6723,156 +6723,156 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C42" t="n">
-        <v>17.903</v>
+        <v>18.121</v>
       </c>
       <c r="D42" t="n">
-        <v>2.774</v>
+        <v>2.939</v>
       </c>
       <c r="E42" t="n">
-        <v>5.226</v>
+        <v>5.364</v>
       </c>
       <c r="F42" t="n">
-        <v>2.613</v>
+        <v>2.606</v>
       </c>
       <c r="G42" t="n">
-        <v>6.645</v>
+        <v>6.636</v>
       </c>
       <c r="H42" t="n">
-        <v>4.516</v>
+        <v>4.424</v>
       </c>
       <c r="I42" t="n">
-        <v>5.032</v>
+        <v>4.909</v>
       </c>
       <c r="J42" t="n">
-        <v>1.742</v>
+        <v>1.697</v>
       </c>
       <c r="K42" t="n">
-        <v>2.871</v>
+        <v>2.848</v>
       </c>
       <c r="L42" t="n">
-        <v>0.71</v>
+        <v>0.758</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.909</v>
       </c>
       <c r="N42" t="n">
-        <v>0.452</v>
+        <v>0.485</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.452</v>
+        <v>1.455</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.452</v>
+        <v>1.455</v>
       </c>
       <c r="R42" t="n">
-        <v>2.194</v>
+        <v>2.242</v>
       </c>
       <c r="S42" t="n">
-        <v>3.645</v>
+        <v>3.576</v>
       </c>
       <c r="T42" t="n">
-        <v>546</v>
+        <v>586</v>
       </c>
       <c r="U42" t="n">
-        <v>2.194</v>
+        <v>2.333</v>
       </c>
       <c r="V42" t="n">
-        <v>1.968</v>
+        <v>2.091</v>
       </c>
       <c r="W42" t="n">
-        <v>1.323</v>
+        <v>1.303</v>
       </c>
       <c r="X42" t="n">
-        <v>0.839</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="Y42" t="n">
-        <v>6</v>
+        <v>5.939</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.968</v>
+        <v>6.848</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.861</v>
+        <v>0.867</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.742</v>
+        <v>0.727</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.645</v>
+        <v>1.606</v>
       </c>
       <c r="AD42" t="n">
-        <v>0.451</v>
+        <v>0.453</v>
       </c>
       <c r="AE42" t="n">
-        <v>0.548</v>
+        <v>0.697</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.645</v>
+        <v>1.818</v>
       </c>
       <c r="AG42" t="n">
-        <v>0.333</v>
+        <v>0.383</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.903</v>
+        <v>0.909</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.645</v>
+        <v>1.727</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.549</v>
+        <v>0.526</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.71</v>
+        <v>1.697</v>
       </c>
       <c r="AL42" t="n">
-        <v>5</v>
+        <v>4.909</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.342</v>
+        <v>0.346</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>15.537</v>
+        <v>15.615</v>
       </c>
       <c r="AP42" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.571</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.636</v>
+        <v>0.64</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.152</v>
+        <v>1.161</v>
       </c>
       <c r="AS42" t="n">
         <v>0.093</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.38</v>
+        <v>0.369</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.311</v>
+        <v>0.314</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.037</v>
+        <v>0.04</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.139</v>
+        <v>0.137</v>
       </c>
       <c r="AY42" t="n">
-        <v>0.066</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="43">
@@ -6882,156 +6882,156 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C43" t="n">
-        <v>7.484</v>
+        <v>7.394</v>
       </c>
       <c r="D43" t="n">
-        <v>2.226</v>
+        <v>2.182</v>
       </c>
       <c r="E43" t="n">
-        <v>4.387</v>
+        <v>4.212</v>
       </c>
       <c r="F43" t="n">
-        <v>0.484</v>
+        <v>0.485</v>
       </c>
       <c r="G43" t="n">
-        <v>1.387</v>
+        <v>1.364</v>
       </c>
       <c r="H43" t="n">
-        <v>1.581</v>
+        <v>1.576</v>
       </c>
       <c r="I43" t="n">
-        <v>1.871</v>
+        <v>1.939</v>
       </c>
       <c r="J43" t="n">
-        <v>2.065</v>
+        <v>2.03</v>
       </c>
       <c r="K43" t="n">
-        <v>2.129</v>
+        <v>2.182</v>
       </c>
       <c r="L43" t="n">
-        <v>0.419</v>
+        <v>0.394</v>
       </c>
       <c r="M43" t="n">
-        <v>0.871</v>
+        <v>0.848</v>
       </c>
       <c r="N43" t="n">
-        <v>0.645</v>
+        <v>0.606</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1.065</v>
+        <v>1.061</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.065</v>
+        <v>1.061</v>
       </c>
       <c r="R43" t="n">
-        <v>1.645</v>
+        <v>1.636</v>
       </c>
       <c r="S43" t="n">
-        <v>2.226</v>
+        <v>2.242</v>
       </c>
       <c r="T43" t="n">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="U43" t="n">
-        <v>1.484</v>
+        <v>1.545</v>
       </c>
       <c r="V43" t="n">
-        <v>0.774</v>
+        <v>0.727</v>
       </c>
       <c r="W43" t="n">
-        <v>0.871</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="X43" t="n">
-        <v>0.548</v>
+        <v>0.515</v>
       </c>
       <c r="Y43" t="n">
-        <v>2.516</v>
+        <v>2.485</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.129</v>
+        <v>3.152</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.804</v>
+        <v>0.788</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.774</v>
+        <v>0.758</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.774</v>
+        <v>1.697</v>
       </c>
       <c r="AD43" t="n">
-        <v>0.436</v>
+        <v>0.446</v>
       </c>
       <c r="AE43" t="n">
-        <v>0.516</v>
+        <v>0.515</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.355</v>
+        <v>1.303</v>
       </c>
       <c r="AG43" t="n">
-        <v>0.381</v>
+        <v>0.395</v>
       </c>
       <c r="AH43" t="n">
-        <v>0.097</v>
+        <v>0.091</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.419</v>
+        <v>0.394</v>
       </c>
       <c r="AJ43" t="n">
         <v>0.231</v>
       </c>
       <c r="AK43" t="n">
-        <v>0.387</v>
+        <v>0.394</v>
       </c>
       <c r="AL43" t="n">
-        <v>0.968</v>
+        <v>0.97</v>
       </c>
       <c r="AM43" t="n">
-        <v>0.4</v>
+        <v>0.406</v>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AO43" t="n">
-        <v>7.662</v>
+        <v>7.49</v>
       </c>
       <c r="AP43" t="n">
-        <v>0.511</v>
+        <v>0.522</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.575</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.977</v>
+        <v>0.987</v>
       </c>
       <c r="AS43" t="n">
-        <v>0.139</v>
+        <v>0.142</v>
       </c>
       <c r="AT43" t="n">
-        <v>0.274</v>
+        <v>0.283</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.939</v>
+        <v>1.914</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.176</v>
+        <v>0.174</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.118</v>
+        <v>0.121</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -7041,156 +7041,156 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C44" t="n">
-        <v>14.429</v>
+        <v>14.087</v>
       </c>
       <c r="D44" t="n">
-        <v>3.19</v>
+        <v>3.043</v>
       </c>
       <c r="E44" t="n">
-        <v>5.19</v>
+        <v>5.043</v>
       </c>
       <c r="F44" t="n">
-        <v>0.857</v>
+        <v>0.913</v>
       </c>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>3.087</v>
       </c>
       <c r="H44" t="n">
-        <v>5.476</v>
+        <v>5.261</v>
       </c>
       <c r="I44" t="n">
-        <v>5.952</v>
+        <v>5.696</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>3.913</v>
       </c>
       <c r="K44" t="n">
-        <v>3.048</v>
+        <v>3.13</v>
       </c>
       <c r="L44" t="n">
-        <v>0.476</v>
+        <v>0.435</v>
       </c>
       <c r="M44" t="n">
-        <v>1.238</v>
+        <v>1.217</v>
       </c>
       <c r="N44" t="n">
-        <v>0.667</v>
+        <v>0.652</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>1.913</v>
       </c>
       <c r="Q44" t="n">
-        <v>2</v>
+        <v>1.913</v>
       </c>
       <c r="R44" t="n">
-        <v>1.429</v>
+        <v>1.391</v>
       </c>
       <c r="S44" t="n">
-        <v>4.619</v>
+        <v>4.435</v>
       </c>
       <c r="T44" t="n">
-        <v>429</v>
+        <v>459</v>
       </c>
       <c r="U44" t="n">
-        <v>2.571</v>
+        <v>2.522</v>
       </c>
       <c r="V44" t="n">
-        <v>1.571</v>
+        <v>1.435</v>
       </c>
       <c r="W44" t="n">
-        <v>0.714</v>
+        <v>0.652</v>
       </c>
       <c r="X44" t="n">
-        <v>0.571</v>
+        <v>0.522</v>
       </c>
       <c r="Y44" t="n">
-        <v>7</v>
+        <v>6.652</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.81</v>
+        <v>7.435</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.896</v>
+        <v>0.895</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.333</v>
+        <v>1.304</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.524</v>
+        <v>2.478</v>
       </c>
       <c r="AD44" t="n">
-        <v>0.528</v>
+        <v>0.526</v>
       </c>
       <c r="AE44" t="n">
-        <v>0.333</v>
+        <v>0.348</v>
       </c>
       <c r="AF44" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.826</v>
       </c>
       <c r="AG44" t="n">
-        <v>0.412</v>
+        <v>0.421</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.143</v>
+        <v>0.174</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.762</v>
+        <v>0.739</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.188</v>
+        <v>0.235</v>
       </c>
       <c r="AK44" t="n">
-        <v>0.714</v>
+        <v>0.739</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.238</v>
+        <v>2.348</v>
       </c>
       <c r="AM44" t="n">
-        <v>0.319</v>
+        <v>0.315</v>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>25:26</t>
+          <t>25:36</t>
         </is>
       </c>
       <c r="AO44" t="n">
-        <v>12.81</v>
+        <v>12.55</v>
       </c>
       <c r="AP44" t="n">
-        <v>0.547</v>
+        <v>0.543</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.667</v>
+        <v>0.662</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.126</v>
+        <v>1.123</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.156</v>
+        <v>0.152</v>
       </c>
       <c r="AT44" t="n">
-        <v>0.669</v>
+        <v>0.647</v>
       </c>
       <c r="AU44" t="n">
-        <v>2</v>
+        <v>2.045</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.226</v>
+        <v>0.221</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.022</v>
+        <v>0.02</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.13</v>
+        <v>0.132</v>
       </c>
       <c r="AY44" t="n">
-        <v>0.145</v>
+        <v>0.142</v>
       </c>
     </row>
     <row r="45">
@@ -7200,16 +7200,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C45" t="n">
-        <v>4.833</v>
+        <v>4.286</v>
       </c>
       <c r="D45" t="n">
-        <v>1.667</v>
+        <v>1.5</v>
       </c>
       <c r="E45" t="n">
-        <v>3.083</v>
+        <v>2.786</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -7218,79 +7218,79 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.5</v>
+        <v>1.286</v>
       </c>
       <c r="I45" t="n">
-        <v>2.833</v>
+        <v>2.429</v>
       </c>
       <c r="J45" t="n">
-        <v>0.25</v>
+        <v>0.286</v>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>1.857</v>
       </c>
       <c r="L45" t="n">
-        <v>1.583</v>
+        <v>1.357</v>
       </c>
       <c r="M45" t="n">
-        <v>0.083</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>1.25</v>
+        <v>1.071</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>0.833</v>
+        <v>0.786</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.833</v>
+        <v>0.786</v>
       </c>
       <c r="R45" t="n">
-        <v>2.167</v>
+        <v>2.286</v>
       </c>
       <c r="S45" t="n">
-        <v>2.083</v>
+        <v>1.786</v>
       </c>
       <c r="T45" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="U45" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="V45" t="n">
-        <v>1.167</v>
+        <v>1</v>
       </c>
       <c r="W45" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="X45" t="n">
-        <v>0.083</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="Y45" t="n">
-        <v>2.833</v>
+        <v>2.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>4.583</v>
+        <v>4</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.618</v>
+        <v>0.625</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AC45" t="n">
-        <v>0.833</v>
+        <v>0.786</v>
       </c>
       <c r="AD45" t="n">
-        <v>0.2</v>
+        <v>0.182</v>
       </c>
       <c r="AE45" t="n">
-        <v>0.167</v>
+        <v>0.143</v>
       </c>
       <c r="AF45" t="n">
-        <v>0.5</v>
+        <v>0.429</v>
       </c>
       <c r="AG45" t="n">
         <v>0.333</v>
@@ -7315,41 +7315,41 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AO45" t="n">
-        <v>5.163</v>
+        <v>4.64</v>
       </c>
       <c r="AP45" t="n">
-        <v>0.541</v>
+        <v>0.538</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.556</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.924</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.161</v>
+        <v>0.169</v>
       </c>
       <c r="AT45" t="n">
-        <v>0.486</v>
+        <v>0.462</v>
       </c>
       <c r="AU45" t="n">
-        <v>0.3</v>
+        <v>0.364</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.187</v>
+        <v>0.183</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AX45" t="n">
         <v>0.175</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.008</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="46">
@@ -7359,156 +7359,156 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C46" t="n">
-        <v>5.091</v>
+        <v>5.083</v>
       </c>
       <c r="D46" t="n">
-        <v>1.091</v>
+        <v>1.042</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>1.917</v>
       </c>
       <c r="F46" t="n">
-        <v>0.864</v>
+        <v>0.875</v>
       </c>
       <c r="G46" t="n">
-        <v>1.909</v>
+        <v>1.875</v>
       </c>
       <c r="H46" t="n">
-        <v>0.318</v>
+        <v>0.375</v>
       </c>
       <c r="I46" t="n">
-        <v>0.545</v>
+        <v>0.583</v>
       </c>
       <c r="J46" t="n">
-        <v>1.273</v>
+        <v>1.25</v>
       </c>
       <c r="K46" t="n">
-        <v>2.318</v>
+        <v>2.208</v>
       </c>
       <c r="L46" t="n">
-        <v>1.182</v>
+        <v>1.167</v>
       </c>
       <c r="M46" t="n">
-        <v>0.591</v>
+        <v>0.583</v>
       </c>
       <c r="N46" t="n">
-        <v>0.182</v>
+        <v>0.167</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="R46" t="n">
-        <v>1.409</v>
+        <v>1.458</v>
       </c>
       <c r="S46" t="n">
-        <v>0.864</v>
+        <v>0.833</v>
       </c>
       <c r="T46" t="n">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="U46" t="n">
-        <v>0.5</v>
+        <v>0.458</v>
       </c>
       <c r="V46" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="W46" t="n">
-        <v>0.318</v>
+        <v>0.292</v>
       </c>
       <c r="X46" t="n">
-        <v>0.182</v>
+        <v>0.167</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.727</v>
+        <v>0.75</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.136</v>
+        <v>1.125</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.64</v>
+        <v>0.667</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.409</v>
+        <v>0.417</v>
       </c>
       <c r="AC46" t="n">
-        <v>0.591</v>
+        <v>0.583</v>
       </c>
       <c r="AD46" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.714</v>
       </c>
       <c r="AE46" t="n">
-        <v>0.273</v>
+        <v>0.25</v>
       </c>
       <c r="AF46" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.792</v>
       </c>
       <c r="AG46" t="n">
-        <v>0.333</v>
+        <v>0.316</v>
       </c>
       <c r="AH46" t="n">
-        <v>0.273</v>
+        <v>0.292</v>
       </c>
       <c r="AI46" t="n">
-        <v>0.727</v>
+        <v>0.75</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0.375</v>
+        <v>0.389</v>
       </c>
       <c r="AK46" t="n">
-        <v>0.591</v>
+        <v>0.583</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.182</v>
+        <v>1.125</v>
       </c>
       <c r="AM46" t="n">
-        <v>0.5</v>
+        <v>0.519</v>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>19:38</t>
+          <t>19:33</t>
         </is>
       </c>
       <c r="AO46" t="n">
-        <v>4.831</v>
+        <v>4.715</v>
       </c>
       <c r="AP46" t="n">
-        <v>0.61</v>
+        <v>0.621</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.613</v>
+        <v>0.628</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.054</v>
+        <v>1.078</v>
       </c>
       <c r="AS46" t="n">
         <v>0.141</v>
       </c>
       <c r="AT46" t="n">
-        <v>0.081</v>
+        <v>0.099</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.867</v>
+        <v>1.875</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.11</v>
+        <v>0.109</v>
       </c>
       <c r="AW46" t="n">
         <v>0.07099999999999999</v>
       </c>
       <c r="AX46" t="n">
-        <v>0.128</v>
+        <v>0.122</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.043</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="47">
@@ -7658,16 +7658,16 @@
         <v>0.85</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.089</v>
+        <v>0.09</v>
       </c>
       <c r="AX47" t="n">
-        <v>0.211</v>
+        <v>0.209</v>
       </c>
       <c r="AY47" t="n">
-        <v>0.029</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="48">
@@ -7817,13 +7817,13 @@
         <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.325</v>
+        <v>0.327</v>
       </c>
       <c r="AW48" t="n">
         <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>0.203</v>
+        <v>0.201</v>
       </c>
       <c r="AY48" t="n">
         <v>0</v>
@@ -7836,153 +7836,153 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C49" t="n">
-        <v>4.188</v>
+        <v>3.941</v>
       </c>
       <c r="D49" t="n">
-        <v>0.625</v>
+        <v>0.588</v>
       </c>
       <c r="E49" t="n">
-        <v>1.594</v>
+        <v>1.529</v>
       </c>
       <c r="F49" t="n">
-        <v>0.875</v>
+        <v>0.824</v>
       </c>
       <c r="G49" t="n">
-        <v>2.281</v>
+        <v>2.176</v>
       </c>
       <c r="H49" t="n">
-        <v>0.312</v>
+        <v>0.294</v>
       </c>
       <c r="I49" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="J49" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="K49" t="n">
-        <v>2</v>
+        <v>1.941</v>
       </c>
       <c r="L49" t="n">
-        <v>0.844</v>
+        <v>0.794</v>
       </c>
       <c r="M49" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="N49" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.188</v>
+        <v>0.176</v>
       </c>
       <c r="R49" t="n">
-        <v>1.312</v>
+        <v>1.235</v>
       </c>
       <c r="S49" t="n">
-        <v>0.406</v>
+        <v>0.382</v>
       </c>
       <c r="T49" t="n">
         <v>146</v>
       </c>
       <c r="U49" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.529</v>
       </c>
       <c r="V49" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.882</v>
       </c>
       <c r="W49" t="n">
-        <v>0.125</v>
+        <v>0.118</v>
       </c>
       <c r="X49" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.594</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.8120000000000001</v>
+        <v>0.765</v>
       </c>
       <c r="AA49" t="n">
         <v>0.731</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.281</v>
+        <v>0.265</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.625</v>
+        <v>0.588</v>
       </c>
       <c r="AD49" t="n">
         <v>0.45</v>
       </c>
       <c r="AE49" t="n">
-        <v>0.062</v>
+        <v>0.059</v>
       </c>
       <c r="AF49" t="n">
-        <v>0.531</v>
+        <v>0.529</v>
       </c>
       <c r="AG49" t="n">
-        <v>0.118</v>
+        <v>0.111</v>
       </c>
       <c r="AH49" t="n">
-        <v>0.375</v>
+        <v>0.353</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.719</v>
+        <v>0.676</v>
       </c>
       <c r="AJ49" t="n">
         <v>0.522</v>
       </c>
       <c r="AK49" t="n">
-        <v>0.5</v>
+        <v>0.471</v>
       </c>
       <c r="AL49" t="n">
-        <v>1.562</v>
+        <v>1.5</v>
       </c>
       <c r="AM49" t="n">
-        <v>0.32</v>
+        <v>0.314</v>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AO49" t="n">
-        <v>4.228</v>
+        <v>4.038</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.5</v>
+        <v>0.492</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.518</v>
+        <v>0.51</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.991</v>
+        <v>0.976</v>
       </c>
       <c r="AS49" t="n">
         <v>0.044</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="AU49" t="n">
         <v>2</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.146</v>
+        <v>0.147</v>
       </c>
       <c r="AW49" t="n">
         <v>0.076</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.167</v>
+        <v>0.169</v>
       </c>
       <c r="AY49" t="n">
         <v>0.012</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.212</v>
+        <v>0.213</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.116</v>
+        <v>0.117</v>
       </c>
       <c r="AX50" t="n">
         <v>0</v>
@@ -8294,13 +8294,13 @@
         <v>0</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.17</v>
+        <v>0.171</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.129</v>
+        <v>0.13</v>
       </c>
       <c r="AX51" t="n">
-        <v>0.12</v>
+        <v>0.119</v>
       </c>
       <c r="AY51" t="n">
         <v>0</v>
@@ -8453,13 +8453,13 @@
         <v>1.125</v>
       </c>
       <c r="AV52" t="n">
-        <v>0.198</v>
+        <v>0.199</v>
       </c>
       <c r="AW52" t="n">
         <v>0.057</v>
       </c>
       <c r="AX52" t="n">
-        <v>0.092</v>
+        <v>0.091</v>
       </c>
       <c r="AY52" t="n">
         <v>0.019</v>
@@ -8612,13 +8612,13 @@
         <v>1</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.267</v>
+        <v>0.268</v>
       </c>
       <c r="AW53" t="n">
         <v>0.051</v>
       </c>
       <c r="AX53" t="n">
-        <v>0.141</v>
+        <v>0.14</v>
       </c>
       <c r="AY53" t="n">
         <v>0.038</v>
@@ -8631,7 +8631,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C54" t="n">
         <v>0</v>
@@ -8658,10 +8658,10 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>1.469</v>
+        <v>1.529</v>
       </c>
       <c r="L54" t="n">
-        <v>1.25</v>
+        <v>1.176</v>
       </c>
       <c r="M54" t="n">
         <v>0</v>
@@ -8673,7 +8673,7 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.656</v>
+        <v>0.676</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -8790,118 +8790,118 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C55" t="n">
-        <v>93.65600000000001</v>
+        <v>93.441</v>
       </c>
       <c r="D55" t="n">
-        <v>21.375</v>
+        <v>21.206</v>
       </c>
       <c r="E55" t="n">
-        <v>37.031</v>
+        <v>36.735</v>
       </c>
       <c r="F55" t="n">
-        <v>10.25</v>
+        <v>10.265</v>
       </c>
       <c r="G55" t="n">
-        <v>27.656</v>
+        <v>27.588</v>
       </c>
       <c r="H55" t="n">
-        <v>20.156</v>
+        <v>20.235</v>
       </c>
       <c r="I55" t="n">
-        <v>25.188</v>
+        <v>25.206</v>
       </c>
       <c r="J55" t="n">
-        <v>17.281</v>
+        <v>17.176</v>
       </c>
       <c r="K55" t="n">
-        <v>26.281</v>
+        <v>26.324</v>
       </c>
       <c r="L55" t="n">
-        <v>10.375</v>
+        <v>10.059</v>
       </c>
       <c r="M55" t="n">
-        <v>7.812</v>
+        <v>7.824</v>
       </c>
       <c r="N55" t="n">
-        <v>6.5</v>
+        <v>6.412</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>13.469</v>
+        <v>13.382</v>
       </c>
       <c r="Q55" t="n">
-        <v>12.812</v>
+        <v>12.706</v>
       </c>
       <c r="R55" t="n">
-        <v>21.969</v>
+        <v>21.971</v>
       </c>
       <c r="S55" t="n">
-        <v>22.656</v>
+        <v>22.647</v>
       </c>
       <c r="T55" t="n">
-        <v>3553</v>
+        <v>3764</v>
       </c>
       <c r="U55" t="n">
-        <v>12.469</v>
+        <v>12.471</v>
       </c>
       <c r="V55" t="n">
-        <v>10.719</v>
+        <v>10.471</v>
       </c>
       <c r="W55" t="n">
-        <v>7.5</v>
+        <v>7.471</v>
       </c>
       <c r="X55" t="n">
-        <v>4.656</v>
+        <v>4.647</v>
       </c>
       <c r="Y55" t="n">
-        <v>32.094</v>
+        <v>32.088</v>
       </c>
       <c r="Z55" t="n">
-        <v>40.406</v>
+        <v>40.235</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.794</v>
+        <v>0.798</v>
       </c>
       <c r="AB55" t="n">
-        <v>6.781</v>
+        <v>6.618</v>
       </c>
       <c r="AC55" t="n">
-        <v>13.469</v>
+        <v>13.265</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.503</v>
+        <v>0.499</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.656</v>
+        <v>2.735</v>
       </c>
       <c r="AF55" t="n">
-        <v>8.343999999999999</v>
+        <v>8.441000000000001</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.318</v>
+        <v>0.324</v>
       </c>
       <c r="AH55" t="n">
-        <v>2.531</v>
+        <v>2.559</v>
       </c>
       <c r="AI55" t="n">
-        <v>6.531</v>
+        <v>6.588</v>
       </c>
       <c r="AJ55" t="n">
         <v>0.388</v>
       </c>
       <c r="AK55" t="n">
-        <v>7.719</v>
+        <v>7.706</v>
       </c>
       <c r="AL55" t="n">
-        <v>21.125</v>
+        <v>21</v>
       </c>
       <c r="AM55" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
@@ -8909,34 +8909,34 @@
         </is>
       </c>
       <c r="AO55" t="n">
-        <v>89.239</v>
+        <v>88.79600000000001</v>
       </c>
       <c r="AP55" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.618</v>
+        <v>0.62</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.05</v>
+        <v>1.052</v>
       </c>
       <c r="AS55" t="n">
         <v>0.151</v>
       </c>
       <c r="AT55" t="n">
-        <v>0.312</v>
+        <v>0.315</v>
       </c>
       <c r="AU55" t="n">
-        <v>1.283</v>
+        <v>1.284</v>
       </c>
       <c r="AV55" t="n">
         <v>0.2</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.061</v>
+        <v>0.059</v>
       </c>
       <c r="AX55" t="n">
-        <v>0.143</v>
+        <v>0.142</v>
       </c>
       <c r="AY55" t="n">
         <v>0</v>
@@ -8949,118 +8949,118 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C56" t="n">
-        <v>86.812</v>
+        <v>86.765</v>
       </c>
       <c r="D56" t="n">
-        <v>22.875</v>
+        <v>22.853</v>
       </c>
       <c r="E56" t="n">
-        <v>42.219</v>
+        <v>42.353</v>
       </c>
       <c r="F56" t="n">
-        <v>8.156000000000001</v>
+        <v>8.206</v>
       </c>
       <c r="G56" t="n">
-        <v>25.031</v>
+        <v>25.118</v>
       </c>
       <c r="H56" t="n">
-        <v>16.594</v>
+        <v>16.441</v>
       </c>
       <c r="I56" t="n">
-        <v>21.375</v>
+        <v>21.294</v>
       </c>
       <c r="J56" t="n">
-        <v>16.719</v>
+        <v>16.882</v>
       </c>
       <c r="K56" t="n">
-        <v>23.75</v>
+        <v>23.765</v>
       </c>
       <c r="L56" t="n">
-        <v>10.594</v>
+        <v>10.824</v>
       </c>
       <c r="M56" t="n">
-        <v>6.719</v>
+        <v>6.735</v>
       </c>
       <c r="N56" t="n">
-        <v>6.406</v>
+        <v>6.294</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>12.906</v>
+        <v>12.941</v>
       </c>
       <c r="Q56" t="n">
-        <v>11.969</v>
+        <v>11.971</v>
       </c>
       <c r="R56" t="n">
         <v>23</v>
       </c>
       <c r="S56" t="n">
-        <v>21.938</v>
+        <v>21.971</v>
       </c>
       <c r="T56" t="n">
-        <v>3073</v>
+        <v>3265</v>
       </c>
       <c r="U56" t="n">
-        <v>10.531</v>
+        <v>10.206</v>
       </c>
       <c r="V56" t="n">
-        <v>10.719</v>
+        <v>10.882</v>
       </c>
       <c r="W56" t="n">
-        <v>5.625</v>
+        <v>5.735</v>
       </c>
       <c r="X56" t="n">
-        <v>3.344</v>
+        <v>3.382</v>
       </c>
       <c r="Y56" t="n">
-        <v>27.688</v>
+        <v>27.412</v>
       </c>
       <c r="Z56" t="n">
-        <v>35.469</v>
+        <v>35.206</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="AB56" t="n">
-        <v>7.469</v>
+        <v>7.588</v>
       </c>
       <c r="AC56" t="n">
-        <v>16.125</v>
+        <v>16.529</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.463</v>
+        <v>0.459</v>
       </c>
       <c r="AE56" t="n">
-        <v>4.312</v>
+        <v>4.294</v>
       </c>
       <c r="AF56" t="n">
-        <v>12</v>
+        <v>11.912</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.312</v>
+        <v>1.324</v>
       </c>
       <c r="AI56" t="n">
-        <v>3.188</v>
+        <v>3.206</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.412</v>
+        <v>0.413</v>
       </c>
       <c r="AK56" t="n">
-        <v>6.844</v>
+        <v>6.882</v>
       </c>
       <c r="AL56" t="n">
-        <v>21.844</v>
+        <v>21.912</v>
       </c>
       <c r="AM56" t="n">
-        <v>0.313</v>
+        <v>0.314</v>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
@@ -9068,34 +9068,34 @@
         </is>
       </c>
       <c r="AO56" t="n">
-        <v>89.56100000000001</v>
+        <v>89.78100000000001</v>
       </c>
       <c r="AP56" t="n">
-        <v>0.522</v>
+        <v>0.521</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AR56" t="n">
-        <v>0.969</v>
+        <v>0.966</v>
       </c>
       <c r="AS56" t="n">
         <v>0.144</v>
       </c>
       <c r="AT56" t="n">
-        <v>0.247</v>
+        <v>0.244</v>
       </c>
       <c r="AU56" t="n">
-        <v>1.295</v>
+        <v>1.305</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.201</v>
+        <v>0.202</v>
       </c>
       <c r="AW56" t="n">
-        <v>0.062</v>
+        <v>0.064</v>
       </c>
       <c r="AX56" t="n">
-        <v>0.129</v>
+        <v>0.128</v>
       </c>
       <c r="AY56" t="n">
         <v>0</v>
